--- a/src/indoor_environment_PyCHAM_setup/indoor_emi_pri_org_VBS.xlsx
+++ b/src/indoor_environment_PyCHAM_setup/indoor_emi_pri_org_VBS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Documents/GitHub/NCAS-BoxModellingToolkit/indoor_environment_PyCHAM_setup/src/indoor_environment_PyCHAM_setup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4E22B8-9761-2B4B-9179-DD6B49E14C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63E5A6B-FED0-9348-BDAA-8DBBD09655F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="620" yWindow="3700" windowWidth="35500" windowHeight="16600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="5900" windowWidth="31060" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="indoor_emi" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="201">
   <si>
     <t>ACRYLONITRILE</t>
   </si>
@@ -449,9 +449,6 @@
     <t>myosmine</t>
   </si>
   <si>
-    <t>Frying (these values represent particles/ or molecules/s/person/meal or mole fraction of particles; particles from 10.1016/j.atmosenv.2010.01.009, using Table 2, which gives units in /min, and so /60 to convert to /s, e.g. 8.02e12 particles/60, gases from https://onlinelibrary.wiley.com/doi/full/10.1111/ina.12906 (Table 4), assuming stir fry lasted 15 minutes, e.g. for ethanol from table 4: ((67.e-3/46.0684)*6.022e23)/(15.*60.), note that citral not in MCM, so represented by limonene).  Particle radius of 0.05 um is the median average particle size when weighted by number concentration in figure 24 of this reference. Black carbon to primary organic mole fractions estimated from Table 18 of http://dx.doi.org/10.1016/j.atmosenv.2013.01.061</t>
-  </si>
-  <si>
     <t>bleach cleaning using Table 2 of https://onlinelibrary.wiley.com/doi/full/10.1111/ina.12906  and assuming cleaning lasts 15 minutes, e.g. for methanol from table 2: ((1.06e-3/32.0419)*6.022e23)/(15.*60.) note that the chloroamines are not included in the MCM, so were omitted</t>
   </si>
   <si>
@@ -491,9 +488,6 @@
     <t>silicon dioxide from indoors</t>
   </si>
   <si>
-    <t>in Table 1 they give the mass fraction of PM10 that is PM2.5 and they give the number of PM10  particles emitted/min emission rate, whilst their Figure  3 indicates that particle number concentration for washable filter bag less vacuum is dominated by PM2.5 (with a mean radius around 0.015 um), which is consistent with Figure 14 of doi.org/10.1016/j.atmosenv.2010.01.009. To get emission rate of PM2.5 particles in number/unit of time, first multiply the mass emission rate of PM10 (ug/s) from their Table 1 by 0.742 (the mass fraction that is PM2.5 from their Table 1), giving 0.93492 ug/s, then get mass of one particle of radius 0.015 um (radius set for vacuum cleaning for PM0 in indoor_emi sheet of this file), assuming a density of 1.4e-6 ug/um3, giving (using mass emission rate of PM10 (ug/s) from the washable filter bag less vacuum in their Table 1): (0.742*1.26)/((4./3.)*np.pi*0.015**3*1.4e-6) = 4.7e10 particles/s of PM2.5 with a mean radius of 0.015 um, likewise, the same can be done for PM2.5-PM10 assuming a mean radius of 2.5 um: ((1.-0.742)*1.26)/((4./3.)*np.pi*2.5**3*1.4e-6) = 3.5e3 particles/s of PM2.5-PM10 with a mean radius of 2.5 um</t>
-  </si>
-  <si>
     <t>nalk_ind_pm0</t>
   </si>
   <si>
@@ -518,9 +512,6 @@
     <t>wood burning stove PM needs updating to Table 4 of https://doi.org/10.1016/j.jobe.2023.107848 (Table 5 of 10.1021/es00161a010), for carbon monoxide (which is given as cm3/h), molar volume (mol/cm3) found using gas-phase density from Wikipedia (1.145e-3 g/cm3) and molar mass (28.010 g/mol), this then multiplied by value in Table V to give mol/h, followed by conversion to molecules/s, the whole equation is (using a mean average of 70 cm3/h from airtight stoves): 70*(1.145e-3/28.010)*6.022e23/3.6e3; for PM1, mg/h converted to particles/s by dividing by mass of one particle of radius 50 nm and density 1.8 g/cm3 (assuming made of black carbon and using density from AeroMix description paper in GMD), and dividing by 60 to convert /min to /s, the whole equation (using the mean TSP (mg/h) from airtight stoves): 4.47e-3/((4./3.)*np.pi*50.e-7**3*1.8)/3600.; for BaP (which is given in ug/h) converted to molecules/cm3/s using the mean average from all airtight stoves: 0.14e-6/252.316*6.022e23/3600.</t>
   </si>
   <si>
-    <t>Smoking Cigarettes (PM: table 2 of 10.1016/j.atmosenv.2010.01.009,  which has units of /min, so /60 to convert to /s (8.83e12/60)), Gases: Table 3 of doi.org/10.1021/es011058w in which ug/cigarette converted to molececules/s/cigarette assuming a cigarette is smoked in 10 minutes), and values taken from the lowest air change rate in Table 3 for a wallboard only room at the lowest air change rate, as these conditions are closest to minimising losses, then the full equation, e.g. for butadiene is: (((350e-6/54.0904)*si.N_A)/(10*60.)). need a reference (and possibly updated values) for particle-phase mole fractions</t>
-  </si>
-  <si>
     <t>candle burning (same ref as smoking) (doi.org/10.1016/j.atmosenv.2010.01.009)</t>
   </si>
   <si>
@@ -531,9 +522,6 @@
   </si>
   <si>
     <t>BZK_ind_pm1</t>
-  </si>
-  <si>
-    <t>page 660 of https://doi.org/10.1080/15459624.2019.1643466 says the mass fraction of cleaning spray emitted on a single spray that goes airbourne (as gas and particles) rather than deposit on the surface to be cleaned is up to 1/3 (backed up by Figure S5 of https://doi.org/10.1016/j.ijheh.2023.114220), also mass of airbourne particles from cleaning spray is small (maximum mass fraction compared to airbourne particles+gas is 0.01%) compared to gas-phase from cleaning spray. Article https://doi.org/10.1016/j.ijheh.2023.114220 says the average emission rate (of total material (airbourne+deposited) is 1.6 g/s of cleaning spray). Suggest the following: convert the size-resolved plots of particle in the paper (Fig. 3 which suggests that the ratio in PM2.5 to PM10 is about 50:50) into an emission rate of particle containing a non-volatile material, and convert the mass of VOC released into individual components based on a mass-weighted ingredient list. This website (https://www.statista.com/statistics/304000/leading-brands-of-household-cleaners-in-the-uk/) suggests Dettol anti-bacterial surface cleanser is one of the best selling in the UK. The back of the dettol bottle lists: benzalkonium chloride as 0.096 % by mass, then there is also an unamed fragrance, sodium bicarbonate, sodium carbonate, sodium edetate, water, C9-C11 alkylpolyglycoside and C12-C16 Pareth-7. I think I can use this article (https://doi.org/10.1039/D2EA00054G) to get the VOC emission rates for commercial cleaning products, and the same article indicates that benzalkonium chloride is non-volatile, so this along with the sodium salts could represent the non-volatile particles</t>
   </si>
   <si>
     <t>Source and Emission Rate (particle/s or molecules/s or mole fractions for particle components)</t>
@@ -587,9 +575,6 @@
     <t>ALLYLAMINE</t>
   </si>
   <si>
-    <t>cleaning spray (https://doi.org/10.1016/j.ijheh.2023.114220 says that the average total mass emission of material from a spray bottle is 1.6 g/s, whilst both the same article and https://doi.org/10.1080/15459624.2019.1643466 say that up to 1/3 of the sprayed material goes airbourne, and the latter study says up to 0.01 % of the airbourne material is particle rather than gas. Therefore, assuming a particle density of 1g/cm^3 and given that Fig. 3 of the latter paper indicates the particle mass is split roughly evenly between PM2.5 and PM10, and assuming a mean radius of the PM2.5 of 1 um and mean radius of the PM10 of 2 um, the equation for pconc in PM2.5 is: (0.0001*(1.6*1./3.)*0.5)/(4./3.*np.pi*1.e-4**3*1.) , whilst for PM10 it is: 0.0001*(1.6*1./3.)*0.5)/(4./3.*np.pi*2.5e-4**3*1.)), and see notes in cleaning_spray_notes sheet for reasoning behind particle composition. Then, rate of VOC emission is given by combining the previously mentioned total emission mass of gas-phase material with mass fractions given in Table 1 of https://doi.org/10.1039/D2EA00054G, e.g. for allylamine ((0.9999*(1.6*1./3.))*0.003e-3/57.09*si.N_A), limonene emission rate based on average factor for general purpose cleaning products (GPC) in Table 6 of  https://doi.org/10.1111/j.1600-0668.2005.00414.x and converted to molecules/s by: (1.6)*10.e-3/136.23*si.N_A</t>
-  </si>
-  <si>
     <t>HEX1ENE</t>
   </si>
   <si>
@@ -613,12 +598,57 @@
   <si>
     <t xml:space="preserve">used as a replacememt for linalool and bornyl acetate, which are not in the MCM, and as a representative of monoterpene alcohols which are reported in natural product mopping emissions </t>
   </si>
+  <si>
+    <t>Smoking Cigarettes (PM: table 2 (particle number) and Fig. 19 (radius) of 10.1016/j.atmosenv.2010.01.009,  which has units of /min, so /60 to convert to /s (8.83e12/60)), Gases: Table 3 of doi.org/10.1021/es011058w in which ug/cigarette converted to molececules/s/cigarette assuming a cigarette is smoked in 10 minutes), and values taken from the lowest air change rate in Table 3 for a wallboard only room at the lowest air change rate, as these conditions are closest to minimising losses, then the full equation, e.g. for butadiene is: (((350e-6/54.0904)*si.N_A)/(10*60.)). need a reference (and possibly updated values) for particle-phase mole fractions</t>
+  </si>
+  <si>
+    <t>in Table 1 they give the mass fraction of PM10 that is PM2.5 and they give the number of PM10  particles emitted/min emission rate, whilst their Figure  3 indicates that particle number concentration for washable filter bag less vacuum is dominated by PM2.5 (with a mean radius around 0.015 um), which is consistent with Figure 14 of doi.org/10.1016/j.atmosenv.2010.01.009. To get emission rate of PM2.5 particles in number/unit of time, first multiply the mass emission rate of PM10 (ug/s) from their Table 1 by 0.742 (the mass fraction that is PM2.5 from their Table 1), giving 0.93492 ug/s, then get mass of one particle of radius 0.015 um (radius set for vacuum cleaning for PM2.5 in indoor_emi sheet of this file), assuming a density of 1.4e-6 ug/um3, giving (using mass emission rate of PM10 (ug/s) from the washable filter bag less vacuum in their Table 1): (0.742*1.26)/((4./3.)*np.pi*0.015**3*1.4e-6) = 4.7e10 particles/s of PM2.5 with a mean radius of 0.015 um, likewise, the same can be done for PM2.5-PM10 assuming a mean radius of 2.5 um: ((1.-0.742)*1.26)/((4./3.)*np.pi*2.5**3*1.4e-6) = 3.5e3 particles/s of PM2.5-PM10 with a mean radius of 2.5 um</t>
+  </si>
+  <si>
+    <t>Frying (these values represent particles/ or molecules/s/person/meal or mole fraction of particles; particles from 10.1016/j.atmosenv.2010.01.009, using Table 2, which gives units in /min, and so /60 to convert to /s, e.g. 8.02e12 particles/60, gases from https://onlinelibrary.wiley.com/doi/full/10.1111/ina.12906 (Table 4), assuming stir fry lasted 15 minutes, e.g. for ethanol from table 4: ((67.e-3/46.0684)*6.022e23)/(15.*60.), note that citral not in MCM, so represented by limonene).  Particle radius of 0.03 um is suggested by Figure 12 of this reference. Black carbon to primary organic mole fractions estimated from Table 18 of http://dx.doi.org/10.1016/j.atmosenv.2013.01.061</t>
+  </si>
+  <si>
+    <t>page 660 of https://doi.org/10.1080/15459624.2019.1643466 says the mass fraction of cleaning spray emitted on a single spray that goes airbourne (as gas and particles) rather than deposit on the surface to be cleaned is up to 1/3 (backed up by Figure S5 of https://doi.org/10.1016/j.ijheh.2023.114220), also mass of airbourne particles from cleaning spray is small (maximum mass fraction compared to airbourne particles+gas is 0.01%) compared to gas-phase from cleaning spray. Article https://doi.org/10.1016/j.ijheh.2023.114220 says the average emission rate (of total material (airbourne+deposited) is 1.6 g/s of cleaning spray). Suggest the following: convert the size-resolved plots of particle in the paper (Fig. 3 which suggests that the ratio in PM2.5 to PM10 is about 50:50) into an emission rate of particle containing a non-volatile material, and convert the mass of VOC released into individual components based on a mass-weighted ingredient list. This website (https://www.statista.com/statistics/304000/leading-brands-of-household-cleaners-in-the-uk/) suggests Dettol anti-bacterial surface cleanser is one of the best selling in the UK. The back of the dettol bottle lists: benzalkonium chloride as 0.096 % by mass, then there is also an unamed fragrance, sodium bicarbonate, sodium carbonate, sodium edetate, water, C9-C11 alkylpolyglycoside and C12-C16 Pareth-7. I think I can use this article (https://doi.org/10.1039/D2EA00054G) to get the VOC emission rates for commercial cleaning products, and the same article indicates that benzalkonium chloride is non-volatile (which the girolami techqnique estimates to have a density of 0.86g/cm^3), so this along with the sodium salts could represent the non-volatile particles</t>
+  </si>
+  <si>
+    <t>cleaning spray (https://doi.org/10.1016/j.ijheh.2023.114220 says that the average total mass emission of material from a spray bottle is 1.6 g/s, whilst both the same article and https://doi.org/10.1080/15459624.2019.1643466 say that up to 1/3 of the sprayed material mass goes airbourne, with a minimum around 4 %, and the latter study says up to 0.01 % of the airbourne material is particle rather than gas, but with a minimum of 0.0001 %. Therefore (using values toward the lower end of fractions going airbourne and fractions of that in the particle-phase), given that Fig. 3 of the latter paper indicates the particle mass is split roughly evenly between PM2.5 and PM10, and assuming a mean radius of the PM2.5 of 1 um and mean radius of the PM10 of 2.5 um, and knowing that the girolami estimation gives a density for BZK of 0.86 g/cm^-3, the equation for pconc in PM2.5 is: (0.0001*(1.6*1./10.)*0.5)/(4./3.*np.pi*1.e-4**3*0.86) , whilst for PM10 it is: (0.0001*(1.6*1./10.)*0.5)/(4./3.*np.pi*2.5e-4**3*0.86), and see notes in cleaning_spray_notes sheet for reasoning behind particle composition. Then, rate of VOC emission is given by combining the previously mentioned total emission mass of gas-phase material with mass fractions given in Table 1 of https://doi.org/10.1039/D2EA00054G, e.g. for allylamine ((0.9999*(1.6*1./10.))*0.003e-3/57.09*si.N_A), limonene emission rate based on average factor for general purpose cleaning products (GPC) in Table 6 of  https://doi.org/10.1111/j.1600-0668.2005.00414.x (typical value around 15mg/g product) and converted to molecules/s by: (0.9999*(1.6*1./10.))*15.e-3/136.23*si.N_A</t>
+  </si>
+  <si>
+    <t>pconc_pm2</t>
+  </si>
+  <si>
+    <t>bcin_pm2</t>
+  </si>
+  <si>
+    <t>nalk_ind_pm2</t>
+  </si>
+  <si>
+    <t>SiO2_ind_pm2</t>
+  </si>
+  <si>
+    <t>BZK_ind_pm2</t>
+  </si>
+  <si>
+    <t>PNNCATCOOH_pm2</t>
+  </si>
+  <si>
+    <t>C1213OH_pm2</t>
+  </si>
+  <si>
+    <t>NLIMOOH_pm2</t>
+  </si>
+  <si>
+    <t>CO25C6CHO_pm2</t>
+  </si>
+  <si>
+    <t>mean_rad_pm2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -639,6 +669,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Menlo"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -682,7 +718,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -691,6 +727,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -710,6 +747,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -994,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P10108"/>
+  <dimension ref="A1:P10118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.5" customWidth="1"/>
@@ -1014,79 +1052,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="8"/>
+      <c r="A1" s="7"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="F2" s="8" t="s">
+      <c r="E2" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="K2" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="O2" s="8" t="s">
+      <c r="L2" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="P2" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>160</v>
-      </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>53</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C3" s="10">
-        <v>0</v>
-      </c>
-      <c r="D3" s="10">
+        <v>146</v>
+      </c>
+      <c r="C3" s="11">
+        <v>0</v>
+      </c>
+      <c r="D3" s="11">
         <v>0</v>
       </c>
       <c r="E3">
@@ -1095,37 +1133,39 @@
       <c r="F3">
         <v>133666666666.7</v>
       </c>
-      <c r="G3" s="8">
-        <v>0</v>
-      </c>
-      <c r="H3" s="8">
-        <v>0</v>
-      </c>
-      <c r="I3" s="8">
-        <v>0</v>
-      </c>
-      <c r="J3" s="8">
+      <c r="G3" s="9">
+        <v>0</v>
+      </c>
+      <c r="H3" s="9">
+        <v>0</v>
+      </c>
+      <c r="I3" s="9">
+        <v>0</v>
+      </c>
+      <c r="J3" s="9">
         <v>1317449251.0999999</v>
       </c>
-      <c r="K3" s="8">
-        <v>0</v>
-      </c>
-      <c r="L3" s="12">
+      <c r="K3" s="9">
+        <v>0</v>
+      </c>
+      <c r="L3" s="13">
         <v>47000000000</v>
       </c>
-      <c r="M3">
-        <v>6366197.7236758098</v>
-      </c>
-      <c r="N3" s="8">
-        <v>0</v>
-      </c>
+      <c r="M3" s="6">
+        <v>0</v>
+      </c>
+      <c r="N3" s="9">
+        <v>0</v>
+      </c>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>64</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4" s="4">
         <v>12.010999999999999</v>
@@ -1163,13 +1203,15 @@
       <c r="N4">
         <v>0</v>
       </c>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C5">
         <v>256.42</v>
@@ -1207,13 +1249,15 @@
       <c r="N5">
         <v>0</v>
       </c>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C6" s="4">
         <v>60.084299999999999</v>
@@ -1251,13 +1295,15 @@
       <c r="N6">
         <v>0</v>
       </c>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C7">
         <v>368.03928000000002</v>
@@ -1290,11 +1336,13 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7">
         <v>0</v>
       </c>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
@@ -1337,6 +1385,8 @@
       <c r="N8">
         <v>0</v>
       </c>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
@@ -1379,6 +1429,8 @@
       <c r="N9">
         <v>0</v>
       </c>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
@@ -1421,6 +1473,8 @@
       <c r="N10">
         <v>0</v>
       </c>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
@@ -1463,22 +1517,24 @@
       <c r="N11">
         <v>0</v>
       </c>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>62</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" s="4">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.3</v>
+        <v>3.9E-2</v>
       </c>
       <c r="F12">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1499,23 +1555,25 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="12" t="s">
         <v>52</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C13" s="4">
-        <v>0</v>
-      </c>
-      <c r="D13" s="4">
+        <v>146</v>
+      </c>
+      <c r="C13" s="11">
+        <v>0</v>
+      </c>
+      <c r="D13" s="11">
         <v>0</v>
       </c>
       <c r="E13">
@@ -1524,37 +1582,37 @@
       <c r="F13">
         <v>0</v>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13" s="12">
-        <v>3500</v>
-      </c>
-      <c r="M13">
-        <v>407436.65431525197</v>
-      </c>
-      <c r="N13">
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>0</v>
+      </c>
+      <c r="I13" s="9">
+        <v>0</v>
+      </c>
+      <c r="J13" s="9">
+        <v>0</v>
+      </c>
+      <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="13">
+        <v>0</v>
+      </c>
+      <c r="M13" s="6">
+        <v>2220766.6477938802</v>
+      </c>
+      <c r="N13" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C14" s="4">
         <v>12.010999999999999</v>
@@ -1563,10 +1621,10 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>9.0899999999999995E-2</v>
+        <v>0</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1595,10 +1653,10 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C15">
         <v>256.42</v>
@@ -1628,7 +1686,7 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -1639,10 +1697,10 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="4">
         <v>60.084299999999999</v>
@@ -1672,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -1683,10 +1741,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C17">
         <v>368.03928000000002</v>
@@ -1782,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>0.18634239288307916</v>
+        <v>0</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1824,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>0.39348119099491646</v>
+        <v>0</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1866,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>0.32927641612200437</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1898,7 +1956,7 @@
         <v>63</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D22" s="4">
         <v>0</v>
@@ -1907,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1925,24 +1983,24 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="N22">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>54</v>
+      <c r="A23" s="12" t="s">
+        <v>191</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="C23" s="4">
-        <v>18.015280000000001</v>
+        <v>0</v>
       </c>
       <c r="D23" s="4">
         <v>0</v>
@@ -1968,25 +2026,25 @@
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
+      <c r="L23" s="13">
+        <v>3500</v>
+      </c>
+      <c r="M23" s="6">
+        <v>142129.06545880801</v>
       </c>
       <c r="N23">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>38</v>
+      <c r="A24" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="C24" s="4">
-        <v>46.025399999999998</v>
+        <v>12.010999999999999</v>
       </c>
       <c r="D24" s="4">
         <v>0</v>
@@ -1995,16 +2053,16 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>9.0899999999999995E-2</v>
       </c>
       <c r="G24">
-        <v>5088253201251670</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
-      <c r="I24" s="12">
-        <v>7.4580997301490002E+18</v>
+      <c r="I24">
+        <v>0</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -2024,13 +2082,13 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>40</v>
+        <v>193</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" s="4">
-        <v>119.3776</v>
+        <v>150</v>
+      </c>
+      <c r="C25">
+        <v>256.42</v>
       </c>
       <c r="D25" s="4">
         <v>0</v>
@@ -2042,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>1289149350929780</v>
+        <v>0</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -2057,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -2068,13 +2126,13 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>23</v>
+        <v>194</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>24</v>
+        <v>148</v>
       </c>
       <c r="C26" s="4">
-        <v>46.068399999999997</v>
+        <v>60.084299999999999</v>
       </c>
       <c r="D26" s="4">
         <v>0</v>
@@ -2082,8 +2140,8 @@
       <c r="E26">
         <v>0</v>
       </c>
-      <c r="F26" s="12">
-        <v>9.7312788037883699E+17</v>
+      <c r="F26">
+        <v>0</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -2091,17 +2149,17 @@
       <c r="H26">
         <v>0</v>
       </c>
-      <c r="I26" s="12">
-        <v>5.8707519291711396E+21</v>
+      <c r="I26">
+        <v>0</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
-        <v>4771231473200710</v>
+        <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -2112,13 +2170,13 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>25</v>
+        <v>195</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="4">
-        <v>32.041899999999998</v>
+        <v>158</v>
+      </c>
+      <c r="C27">
+        <v>368.03928000000002</v>
       </c>
       <c r="D27" s="4">
         <v>0</v>
@@ -2126,11 +2184,11 @@
       <c r="E27">
         <v>0</v>
       </c>
-      <c r="F27" s="12">
-        <v>8.9794231234033504E+16</v>
-      </c>
-      <c r="G27" s="12">
-        <v>2.2135322118157E+16</v>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -2148,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -2156,13 +2214,11 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="4">
-        <v>60.052</v>
+        <v>196</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28">
+        <v>324.19839999999999</v>
       </c>
       <c r="D28" s="4">
         <v>0</v>
@@ -2170,8 +2226,8 @@
       <c r="E28">
         <v>0</v>
       </c>
-      <c r="F28" s="12">
-        <v>3.89976834891242E+16</v>
+      <c r="F28">
+        <v>0</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -2179,7 +2235,7 @@
       <c r="H28">
         <v>0</v>
       </c>
-      <c r="I28" s="12">
+      <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
@@ -2200,13 +2256,11 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" s="4">
-        <v>44.052599999999998</v>
+        <v>197</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29">
+        <v>260.28359999999998</v>
       </c>
       <c r="D29" s="4">
         <v>0</v>
@@ -2214,17 +2268,17 @@
       <c r="E29">
         <v>0</v>
       </c>
-      <c r="F29" s="12">
-        <v>2.56692630577486E+16</v>
-      </c>
-      <c r="G29" s="12">
-        <v>1.57964695739991E+16</v>
+      <c r="F29">
+        <v>0.18634239288307916</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
       </c>
       <c r="H29">
         <v>0</v>
       </c>
-      <c r="I29" s="12">
-        <v>1.7593729219433099E+19</v>
+      <c r="I29">
+        <v>0</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -2244,13 +2298,11 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="4">
-        <v>58.079099999999997</v>
+        <v>198</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30">
+        <v>231.2457</v>
       </c>
       <c r="D30" s="4">
         <v>0</v>
@@ -2258,17 +2310,17 @@
       <c r="E30">
         <v>0</v>
       </c>
-      <c r="F30" s="12">
-        <v>1.47464788921009E+16</v>
+      <c r="F30">
+        <v>0.39348119099491646</v>
       </c>
       <c r="G30">
-        <v>8986135574874030</v>
+        <v>0</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
-      <c r="I30" s="12">
-        <v>1.88E+19</v>
+      <c r="I30">
+        <v>0</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -2288,13 +2340,11 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="4">
-        <v>72.105699999999999</v>
+        <v>199</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31">
+        <v>142.1525</v>
       </c>
       <c r="D31" s="4">
         <v>0</v>
@@ -2303,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>4918181071522620</v>
+        <v>0.32927641612200437</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -2311,7 +2361,7 @@
       <c r="H31">
         <v>0</v>
       </c>
-      <c r="I31" s="12">
+      <c r="I31">
         <v>0</v>
       </c>
       <c r="J31">
@@ -2332,30 +2382,27 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>11</v>
+        <v>200</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C32" s="4">
-        <v>54.090400000000002</v>
+        <v>147</v>
       </c>
       <c r="D32" s="4">
         <v>0</v>
       </c>
-      <c r="E32" s="12">
-        <v>6494526650446900</v>
-      </c>
-      <c r="F32" s="12">
-        <v>0</v>
-      </c>
-      <c r="G32" s="12">
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>2.5</v>
+      </c>
+      <c r="G32">
         <v>0</v>
       </c>
       <c r="H32">
         <v>0</v>
       </c>
-      <c r="I32" s="12">
+      <c r="I32">
         <v>0</v>
       </c>
       <c r="J32">
@@ -2365,10 +2412,10 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -2376,31 +2423,31 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="C33" s="4">
-        <v>68.117000000000004</v>
+        <v>18.015280000000001</v>
       </c>
       <c r="D33" s="4">
         <v>0</v>
       </c>
-      <c r="E33" s="12">
-        <v>4.05206901116216E+16</v>
+      <c r="E33">
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>3438038799255520</v>
-      </c>
-      <c r="G33" s="12">
+        <v>0</v>
+      </c>
+      <c r="G33">
         <v>0</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
-      <c r="I33" s="12">
-        <v>2.7450925701073101E+18</v>
+      <c r="I33">
+        <v>0</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -2420,31 +2467,31 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C34" s="4">
-        <v>56.063299999999998</v>
+        <v>46.025399999999998</v>
       </c>
       <c r="D34" s="4">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>9846540779202550</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>6683556305501490</v>
-      </c>
-      <c r="G34" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>5088253201251670</v>
       </c>
       <c r="H34">
         <v>0</v>
       </c>
-      <c r="I34" s="12">
-        <v>0</v>
+      <c r="I34" s="13">
+        <v>7.4580997301490002E+18</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -2464,30 +2511,30 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>115</v>
+        <v>41</v>
       </c>
       <c r="C35" s="4">
-        <v>53.064</v>
+        <v>119.3776</v>
       </c>
       <c r="D35" s="4">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>3612709448841650</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>0</v>
       </c>
-      <c r="G35" s="12">
-        <v>0</v>
+      <c r="G35">
+        <v>1289149350929780</v>
       </c>
       <c r="H35">
         <v>0</v>
       </c>
-      <c r="I35" s="12">
+      <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
@@ -2508,37 +2555,37 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="C36" s="4">
-        <v>72.105699999999999</v>
+        <v>46.068399999999997</v>
       </c>
       <c r="D36" s="4">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>3855758491862170</v>
-      </c>
-      <c r="F36" s="12">
-        <v>0</v>
-      </c>
-      <c r="G36" s="12">
+        <v>0</v>
+      </c>
+      <c r="F36" s="13">
+        <v>9.7312788037883699E+17</v>
+      </c>
+      <c r="G36">
         <v>0</v>
       </c>
       <c r="H36">
         <v>0</v>
       </c>
-      <c r="I36" s="12">
-        <v>0</v>
+      <c r="I36" s="13">
+        <v>5.8707519291711396E+21</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>4771231473200710</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -2552,30 +2599,30 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>117</v>
+        <v>26</v>
       </c>
       <c r="C37" s="4">
-        <v>41.052999999999997</v>
+        <v>32.041899999999998</v>
       </c>
       <c r="D37" s="4">
         <v>0</v>
       </c>
-      <c r="E37" s="12">
-        <v>2.30306213752953E+16</v>
-      </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37" s="12">
-        <v>0</v>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37" s="13">
+        <v>8.9794231234033504E+16</v>
+      </c>
+      <c r="G37" s="13">
+        <v>2.2135322118157E+16</v>
       </c>
       <c r="H37">
         <v>0</v>
       </c>
-      <c r="I37" s="12">
+      <c r="I37">
         <v>0</v>
       </c>
       <c r="J37">
@@ -2596,31 +2643,31 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="C38" s="4">
-        <v>78.111800000000002</v>
+        <v>60.052</v>
       </c>
       <c r="D38" s="4">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>4972719602159980</v>
-      </c>
-      <c r="F38" s="12">
-        <v>0</v>
-      </c>
-      <c r="G38" s="12">
+        <v>0</v>
+      </c>
+      <c r="F38" s="13">
+        <v>3.89976834891242E+16</v>
+      </c>
+      <c r="G38">
         <v>0</v>
       </c>
       <c r="H38">
         <v>0</v>
       </c>
-      <c r="I38" s="12">
-        <v>2.8332937268120801E+18</v>
+      <c r="I38" s="13">
+        <v>0</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -2631,8 +2678,8 @@
       <c r="L38">
         <v>0</v>
       </c>
-      <c r="M38" s="12">
-        <v>8.6341354134360197E+18</v>
+      <c r="M38">
+        <v>0</v>
       </c>
       <c r="N38">
         <v>0</v>
@@ -2640,31 +2687,31 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="C39" s="4">
-        <v>92.138400000000004</v>
+        <v>44.052599999999998</v>
       </c>
       <c r="D39" s="4">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>8878029716527880</v>
-      </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-      <c r="G39" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="F39" s="13">
+        <v>2.56692630577486E+16</v>
+      </c>
+      <c r="G39" s="13">
+        <v>1.57964695739991E+16</v>
       </c>
       <c r="H39">
-        <v>1328950072210210</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I39" s="13">
+        <v>1.7593729219433099E+19</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -2684,31 +2731,31 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="C40" s="4">
-        <v>106.16500000000001</v>
+        <v>58.079099999999997</v>
       </c>
       <c r="D40" s="4">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>1181757319581150</v>
-      </c>
-      <c r="F40" s="12">
-        <v>0</v>
-      </c>
-      <c r="G40" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="F40" s="13">
+        <v>1.47464788921009E+16</v>
+      </c>
+      <c r="G40">
+        <v>8986135574874030</v>
       </c>
       <c r="H40">
         <v>0</v>
       </c>
-      <c r="I40" s="12">
-        <v>0</v>
+      <c r="I40" s="13">
+        <v>1.88E+19</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -2728,30 +2775,30 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="C41" s="4">
-        <v>106.16500000000001</v>
+        <v>72.105699999999999</v>
       </c>
       <c r="D41" s="4">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>3403461080393720</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>0</v>
-      </c>
-      <c r="G41" s="12">
+        <v>4918181071522620</v>
+      </c>
+      <c r="G41">
         <v>0</v>
       </c>
       <c r="H41">
         <v>0</v>
       </c>
-      <c r="I41" s="12">
+      <c r="I41" s="13">
         <v>0</v>
       </c>
       <c r="J41">
@@ -2772,30 +2819,30 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C42" s="4">
-        <v>106.16500000000001</v>
+        <v>54.090400000000002</v>
       </c>
       <c r="D42" s="4">
         <v>0</v>
       </c>
-      <c r="E42">
-        <v>671238157522096</v>
-      </c>
-      <c r="F42" s="12">
-        <v>0</v>
-      </c>
-      <c r="G42" s="12">
+      <c r="E42" s="13">
+        <v>6494526650446900</v>
+      </c>
+      <c r="F42" s="13">
+        <v>0</v>
+      </c>
+      <c r="G42" s="13">
         <v>0</v>
       </c>
       <c r="H42">
         <v>0</v>
       </c>
-      <c r="I42" s="12">
+      <c r="I42" s="13">
         <v>0</v>
       </c>
       <c r="J42">
@@ -2816,31 +2863,31 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="C43" s="4">
-        <v>104.1491</v>
+        <v>68.117000000000004</v>
       </c>
       <c r="D43" s="4">
         <v>0</v>
       </c>
-      <c r="E43">
-        <v>1657572670207100</v>
+      <c r="E43" s="13">
+        <v>4.05206901116216E+16</v>
       </c>
       <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43" s="12">
+        <v>3438038799255520</v>
+      </c>
+      <c r="G43" s="13">
         <v>0</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
-      <c r="I43" s="12">
-        <v>0</v>
+      <c r="I43" s="13">
+        <v>2.7450925701073101E+18</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -2860,30 +2907,30 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="C44" s="4">
-        <v>120.19159999999999</v>
+        <v>56.063299999999998</v>
       </c>
       <c r="D44" s="4">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>459291306269878</v>
-      </c>
-      <c r="F44" s="12">
-        <v>0</v>
-      </c>
-      <c r="G44" s="12">
+        <v>9846540779202550</v>
+      </c>
+      <c r="F44">
+        <v>6683556305501490</v>
+      </c>
+      <c r="G44" s="13">
         <v>0</v>
       </c>
       <c r="H44">
         <v>0</v>
       </c>
-      <c r="I44" s="12">
+      <c r="I44" s="13">
         <v>0</v>
       </c>
       <c r="J44">
@@ -2904,30 +2951,30 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C45" s="4">
-        <v>128.1705</v>
+        <v>53.064</v>
       </c>
       <c r="D45" s="4">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>203603350953092</v>
+        <v>3612709448841650</v>
       </c>
       <c r="F45">
         <v>0</v>
       </c>
-      <c r="G45" s="12">
+      <c r="G45" s="13">
         <v>0</v>
       </c>
       <c r="H45">
         <v>0</v>
       </c>
-      <c r="I45" s="12">
+      <c r="I45" s="13">
         <v>0</v>
       </c>
       <c r="J45">
@@ -2948,30 +2995,30 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C46" s="4">
-        <v>142.20099999999999</v>
+        <v>72.105699999999999</v>
       </c>
       <c r="D46" s="4">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>115049465648389</v>
-      </c>
-      <c r="F46" s="12">
-        <v>0</v>
-      </c>
-      <c r="G46" s="12">
+        <v>3855758491862170</v>
+      </c>
+      <c r="F46" s="13">
+        <v>0</v>
+      </c>
+      <c r="G46" s="13">
         <v>0</v>
       </c>
       <c r="H46">
         <v>0</v>
       </c>
-      <c r="I46" s="12">
+      <c r="I46" s="13">
         <v>0</v>
       </c>
       <c r="J46">
@@ -2992,30 +3039,30 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C47" s="4">
-        <v>142.20099999999999</v>
+        <v>41.052999999999997</v>
       </c>
       <c r="D47" s="4">
         <v>0</v>
       </c>
-      <c r="E47">
-        <v>110814515992620</v>
+      <c r="E47" s="13">
+        <v>2.30306213752953E+16</v>
       </c>
       <c r="F47">
         <v>0</v>
       </c>
-      <c r="G47" s="12">
+      <c r="G47" s="13">
         <v>0</v>
       </c>
       <c r="H47">
         <v>0</v>
       </c>
-      <c r="I47" s="12">
+      <c r="I47" s="13">
         <v>0</v>
       </c>
       <c r="J47">
@@ -3036,31 +3083,31 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="C48" s="4">
-        <v>94.111199999999997</v>
+        <v>78.111800000000002</v>
       </c>
       <c r="D48" s="4">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>885189865959984</v>
-      </c>
-      <c r="F48" s="12">
-        <v>0</v>
-      </c>
-      <c r="G48" s="12">
+        <v>4972719602159980</v>
+      </c>
+      <c r="F48" s="13">
+        <v>0</v>
+      </c>
+      <c r="G48" s="13">
         <v>0</v>
       </c>
       <c r="H48">
         <v>0</v>
       </c>
-      <c r="I48" s="12">
-        <v>0</v>
+      <c r="I48" s="13">
+        <v>2.8332937268120801E+18</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -3071,8 +3118,8 @@
       <c r="L48">
         <v>0</v>
       </c>
-      <c r="M48" s="12">
-        <v>1.3308681516865201E+18</v>
+      <c r="M48" s="14">
+        <v>2.59018093480173E+18</v>
       </c>
       <c r="N48">
         <v>0</v>
@@ -3080,30 +3127,30 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C49" s="4">
-        <v>108.1378</v>
+        <v>92.138400000000004</v>
       </c>
       <c r="D49" s="4">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>130870341231280</v>
+        <v>8878029716527880</v>
       </c>
       <c r="F49">
         <v>0</v>
       </c>
-      <c r="G49" s="12">
+      <c r="G49" s="13">
         <v>0</v>
       </c>
       <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49" s="12">
+        <v>1328950072210210</v>
+      </c>
+      <c r="I49">
         <v>0</v>
       </c>
       <c r="J49">
@@ -3124,30 +3171,30 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>56</v>
+        <v>119</v>
       </c>
       <c r="C50" s="4">
-        <v>108.1378</v>
+        <v>106.16500000000001</v>
       </c>
       <c r="D50" s="4">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>213476443143224</v>
-      </c>
-      <c r="F50" s="12">
-        <v>0</v>
-      </c>
-      <c r="G50" s="12">
+        <v>1181757319581150</v>
+      </c>
+      <c r="F50" s="13">
+        <v>0</v>
+      </c>
+      <c r="G50" s="13">
         <v>0</v>
       </c>
       <c r="H50">
         <v>0</v>
       </c>
-      <c r="I50" s="12">
+      <c r="I50" s="13">
         <v>0</v>
       </c>
       <c r="J50">
@@ -3168,30 +3215,30 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C51" s="4">
-        <v>79.099999999999994</v>
+        <v>106.16500000000001</v>
       </c>
       <c r="D51" s="4">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>4580684396038760</v>
+        <v>3403461080393720</v>
       </c>
       <c r="F51">
         <v>0</v>
       </c>
-      <c r="G51" s="12">
+      <c r="G51" s="13">
         <v>0</v>
       </c>
       <c r="H51">
         <v>0</v>
       </c>
-      <c r="I51" s="12">
+      <c r="I51" s="13">
         <v>0</v>
       </c>
       <c r="J51">
@@ -3212,30 +3259,30 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C52" s="4">
-        <v>93.13</v>
+        <v>106.16500000000001</v>
       </c>
       <c r="D52" s="4">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>1422603851820030</v>
-      </c>
-      <c r="F52" s="12">
-        <v>0</v>
-      </c>
-      <c r="G52" s="12">
+        <v>671238157522096</v>
+      </c>
+      <c r="F52" s="13">
+        <v>0</v>
+      </c>
+      <c r="G52" s="13">
         <v>0</v>
       </c>
       <c r="H52">
         <v>0</v>
       </c>
-      <c r="I52" s="12">
+      <c r="I52" s="13">
         <v>0</v>
       </c>
       <c r="J52">
@@ -3256,30 +3303,30 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C53" s="4">
-        <v>93.13</v>
+        <v>104.1491</v>
       </c>
       <c r="D53" s="4">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>3103862949425530</v>
+        <v>1657572670207100</v>
       </c>
       <c r="F53">
         <v>0</v>
       </c>
-      <c r="G53" s="12">
+      <c r="G53" s="13">
         <v>0</v>
       </c>
       <c r="H53">
         <v>0</v>
       </c>
-      <c r="I53" s="12">
+      <c r="I53" s="13">
         <v>0</v>
       </c>
       <c r="J53">
@@ -3300,30 +3347,30 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C54" s="4">
-        <v>67.09</v>
+        <v>120.19159999999999</v>
       </c>
       <c r="D54" s="4">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>4144017962239770</v>
-      </c>
-      <c r="F54" s="12">
-        <v>0</v>
-      </c>
-      <c r="G54" s="12">
+        <v>459291306269878</v>
+      </c>
+      <c r="F54" s="13">
+        <v>0</v>
+      </c>
+      <c r="G54" s="13">
         <v>0</v>
       </c>
       <c r="H54">
         <v>0</v>
       </c>
-      <c r="I54" s="12">
+      <c r="I54" s="13">
         <v>0</v>
       </c>
       <c r="J54">
@@ -3344,30 +3391,30 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C55" s="4">
-        <v>105.13720000000001</v>
+        <v>128.1705</v>
       </c>
       <c r="D55" s="4">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>4572763690428630</v>
+        <v>203603350953092</v>
       </c>
       <c r="F55">
         <v>0</v>
       </c>
-      <c r="G55" s="12">
+      <c r="G55" s="13">
         <v>0</v>
       </c>
       <c r="H55">
         <v>0</v>
       </c>
-      <c r="I55" s="12">
+      <c r="I55" s="13">
         <v>0</v>
       </c>
       <c r="J55">
@@ -3388,30 +3435,30 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C56" s="4">
-        <v>162.23599999999999</v>
+        <v>142.20099999999999</v>
       </c>
       <c r="D56" s="4">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>9898568768132020</v>
-      </c>
-      <c r="F56" s="12">
-        <v>0</v>
-      </c>
-      <c r="G56" s="12">
+        <v>115049465648389</v>
+      </c>
+      <c r="F56" s="13">
+        <v>0</v>
+      </c>
+      <c r="G56" s="13">
         <v>0</v>
       </c>
       <c r="H56">
         <v>0</v>
       </c>
-      <c r="I56" s="12">
+      <c r="I56" s="13">
         <v>0</v>
       </c>
       <c r="J56">
@@ -3432,30 +3479,30 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C57" s="4">
-        <v>146.19300000000001</v>
+        <v>142.20099999999999</v>
       </c>
       <c r="D57" s="4">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>459989455628290</v>
+        <v>110814515992620</v>
       </c>
       <c r="F57">
         <v>0</v>
       </c>
-      <c r="G57" s="12">
+      <c r="G57" s="13">
         <v>0</v>
       </c>
       <c r="H57">
         <v>0</v>
       </c>
-      <c r="I57" s="12">
+      <c r="I57" s="13">
         <v>0</v>
       </c>
       <c r="J57">
@@ -3476,74 +3523,74 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>34</v>
+        <v>127</v>
       </c>
       <c r="C58" s="4">
-        <v>136.23400000000001</v>
+        <v>94.111199999999997</v>
       </c>
       <c r="D58" s="4">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>0</v>
-      </c>
-      <c r="F58">
-        <v>2996005239351240</v>
-      </c>
-      <c r="G58" s="12">
-        <v>0</v>
-      </c>
-      <c r="H58" s="12">
-        <v>6.13935499867058E+16</v>
-      </c>
-      <c r="I58">
+        <v>885189865959984</v>
+      </c>
+      <c r="F58" s="13">
+        <v>0</v>
+      </c>
+      <c r="G58" s="13">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58" s="13">
         <v>0</v>
       </c>
       <c r="J58">
         <v>0</v>
       </c>
       <c r="K58">
-        <v>8929077910066500</v>
+        <v>0</v>
       </c>
       <c r="L58">
         <v>0</v>
       </c>
-      <c r="M58" s="12">
-        <v>7.0729099434779402E+19</v>
+      <c r="M58" s="14">
+        <v>3.9925535458655002E+17</v>
       </c>
       <c r="N58">
-        <v>2343310730695090</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" t="s">
-        <v>43</v>
+        <v>18</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>128</v>
       </c>
       <c r="C59" s="4">
-        <v>82.100499999999997</v>
+        <v>108.1378</v>
       </c>
       <c r="D59" s="4">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>130870341231280</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
-      <c r="G59" s="12">
+      <c r="G59" s="13">
         <v>0</v>
       </c>
       <c r="H59">
-        <v>2607968959452810</v>
-      </c>
-      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="I59" s="13">
         <v>0</v>
       </c>
       <c r="J59">
@@ -3564,30 +3611,30 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C60" s="4">
-        <v>60.094999999999999</v>
+        <v>108.1378</v>
       </c>
       <c r="D60" s="4">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>0</v>
-      </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="G60" s="12">
+        <v>213476443143224</v>
+      </c>
+      <c r="F60" s="13">
+        <v>0</v>
+      </c>
+      <c r="G60" s="13">
         <v>0</v>
       </c>
       <c r="H60">
         <v>0</v>
       </c>
-      <c r="I60" s="12">
+      <c r="I60" s="13">
         <v>0</v>
       </c>
       <c r="J60">
@@ -3608,34 +3655,34 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>47</v>
+        <v>129</v>
       </c>
       <c r="C61" s="4">
-        <v>28.01</v>
+        <v>79.099999999999994</v>
       </c>
       <c r="D61" s="4">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>4580684396038760</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
-      <c r="G61" s="12">
+      <c r="G61" s="13">
         <v>0</v>
       </c>
       <c r="H61">
         <v>0</v>
       </c>
-      <c r="I61" s="12">
-        <v>0</v>
-      </c>
-      <c r="J61" s="12">
-        <v>4.7866168828592902E+17</v>
+      <c r="I61" s="13">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
       </c>
       <c r="K61">
         <v>0</v>
@@ -3652,34 +3699,34 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="C62" s="4">
-        <v>252.316</v>
+        <v>93.13</v>
       </c>
       <c r="D62" s="4">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0</v>
-      </c>
-      <c r="F62">
-        <v>0</v>
-      </c>
-      <c r="G62" s="12">
+        <v>1422603851820030</v>
+      </c>
+      <c r="F62" s="13">
+        <v>0</v>
+      </c>
+      <c r="G62" s="13">
         <v>0</v>
       </c>
       <c r="H62">
         <v>0</v>
       </c>
-      <c r="I62" s="12">
+      <c r="I62" s="13">
         <v>0</v>
       </c>
       <c r="J62">
-        <v>92815710810.606094</v>
+        <v>0</v>
       </c>
       <c r="K62">
         <v>0</v>
@@ -3696,37 +3743,37 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="C63" s="4">
-        <v>108.1378</v>
+        <v>93.13</v>
       </c>
       <c r="D63" s="4">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>3103862949425530</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
-      <c r="G63" s="12">
+      <c r="G63" s="13">
         <v>0</v>
       </c>
       <c r="H63">
         <v>0</v>
       </c>
-      <c r="I63" s="12">
+      <c r="I63" s="13">
         <v>0</v>
       </c>
       <c r="J63">
         <v>0</v>
       </c>
       <c r="K63">
-        <v>6626896422897450</v>
+        <v>0</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -3740,31 +3787,31 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="C64" s="4">
-        <v>88.148200000000003</v>
+        <v>67.09</v>
       </c>
       <c r="D64" s="4">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
-      </c>
-      <c r="F64">
-        <v>0</v>
-      </c>
-      <c r="G64" s="12">
+        <v>4144017962239770</v>
+      </c>
+      <c r="F64" s="13">
+        <v>0</v>
+      </c>
+      <c r="G64" s="13">
         <v>0</v>
       </c>
       <c r="H64">
         <v>0</v>
       </c>
-      <c r="I64" s="12">
-        <v>7.99324851692944E+17</v>
+      <c r="I64" s="13">
+        <v>0</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -3783,32 +3830,32 @@
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>98</v>
+      <c r="A65" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C65">
-        <v>76.094399999999993</v>
+        <v>133</v>
+      </c>
+      <c r="C65" s="4">
+        <v>105.13720000000001</v>
       </c>
       <c r="D65" s="4">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>4572763690428630</v>
       </c>
       <c r="F65">
         <v>0</v>
       </c>
-      <c r="G65" s="12">
+      <c r="G65" s="13">
         <v>0</v>
       </c>
       <c r="H65">
         <v>0</v>
       </c>
-      <c r="I65" s="12">
-        <v>2.8727962844572001E+18</v>
+      <c r="I65" s="13">
+        <v>0</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -3828,31 +3875,31 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>101</v>
+        <v>9</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C66">
-        <v>100.1589</v>
+        <v>134</v>
+      </c>
+      <c r="C66" s="4">
+        <v>162.23599999999999</v>
       </c>
       <c r="D66" s="4">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>0</v>
-      </c>
-      <c r="F66">
-        <v>0</v>
-      </c>
-      <c r="G66" s="12">
+        <v>9898568768132020</v>
+      </c>
+      <c r="F66" s="13">
+        <v>0</v>
+      </c>
+      <c r="G66" s="13">
         <v>0</v>
       </c>
       <c r="H66">
         <v>0</v>
       </c>
-      <c r="I66" s="12">
-        <v>2.1374745930516401E+18</v>
+      <c r="I66" s="13">
+        <v>0</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -3871,32 +3918,32 @@
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>103</v>
+      <c r="A67" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C67">
-        <v>114.1855</v>
+        <v>135</v>
+      </c>
+      <c r="C67" s="4">
+        <v>146.19300000000001</v>
       </c>
       <c r="D67" s="4">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>459989455628290</v>
       </c>
       <c r="F67">
         <v>0</v>
       </c>
-      <c r="G67" s="12">
+      <c r="G67" s="13">
         <v>0</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
-      <c r="I67" s="12">
-        <v>7.0407870654329997E+17</v>
+      <c r="I67" s="13">
+        <v>0</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -3916,12 +3963,12 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C68">
+        <v>34</v>
+      </c>
+      <c r="C68" s="4">
         <v>136.23400000000001</v>
       </c>
       <c r="D68" s="4">
@@ -3931,42 +3978,42 @@
         <v>0</v>
       </c>
       <c r="F68">
-        <v>0</v>
-      </c>
-      <c r="G68" s="12">
-        <v>0</v>
-      </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
-      <c r="I68" s="12">
-        <v>3.2841650965559202E+19</v>
+        <v>2996005239351240</v>
+      </c>
+      <c r="G68" s="13">
+        <v>0</v>
+      </c>
+      <c r="H68" s="13">
+        <v>6.13935499867058E+16</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
       </c>
       <c r="J68">
         <v>0</v>
       </c>
       <c r="K68">
-        <v>0</v>
+        <v>8929077910066500</v>
       </c>
       <c r="L68">
         <v>0</v>
       </c>
-      <c r="M68">
-        <v>0</v>
+      <c r="M68" s="14">
+        <v>1.06083039787253E+19</v>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>2343310730695090</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>107</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C69">
-        <v>170.24870000000001</v>
+      <c r="A69" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B69" t="s">
+        <v>43</v>
+      </c>
+      <c r="C69" s="4">
+        <v>82.100499999999997</v>
       </c>
       <c r="D69" s="4">
         <v>0</v>
@@ -3977,14 +4024,14 @@
       <c r="F69">
         <v>0</v>
       </c>
-      <c r="G69" s="12">
+      <c r="G69" s="13">
         <v>0</v>
       </c>
       <c r="H69">
-        <v>1375569322343650</v>
-      </c>
-      <c r="I69" s="12">
-        <v>5.9956572873684198E+17</v>
+        <v>2607968959452810</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -3998,19 +4045,19 @@
       <c r="M69">
         <v>0</v>
       </c>
-      <c r="N69" s="12">
-        <v>2.48918362198186E+16</v>
+      <c r="N69">
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>108</v>
+      <c r="A70" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C70">
-        <v>170.24870000000001</v>
+        <v>45</v>
+      </c>
+      <c r="C70" s="4">
+        <v>60.094999999999999</v>
       </c>
       <c r="D70" s="4">
         <v>0</v>
@@ -4021,14 +4068,14 @@
       <c r="F70">
         <v>0</v>
       </c>
-      <c r="G70" s="12">
+      <c r="G70" s="13">
         <v>0</v>
       </c>
       <c r="H70">
         <v>0</v>
       </c>
-      <c r="I70" s="12">
-        <v>4.4569487799906803E+17</v>
+      <c r="I70" s="13">
+        <v>0</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -4048,13 +4095,13 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C71">
-        <v>204.3511</v>
+        <v>47</v>
+      </c>
+      <c r="C71" s="4">
+        <v>28.01</v>
       </c>
       <c r="D71" s="4">
         <v>0</v>
@@ -4065,17 +4112,17 @@
       <c r="F71">
         <v>0</v>
       </c>
-      <c r="G71" s="12">
+      <c r="G71" s="13">
         <v>0</v>
       </c>
       <c r="H71">
         <v>0</v>
       </c>
-      <c r="I71" s="12">
-        <v>5.59185249900783E+18</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
+      <c r="I71" s="13">
+        <v>0</v>
+      </c>
+      <c r="J71" s="13">
+        <v>4.7866168828592902E+17</v>
       </c>
       <c r="K71">
         <v>0</v>
@@ -4092,13 +4139,13 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B72" t="s">
-        <v>166</v>
-      </c>
-      <c r="C72">
-        <v>57.09</v>
+        <v>48</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C72" s="4">
+        <v>252.316</v>
       </c>
       <c r="D72" s="4">
         <v>0</v>
@@ -4109,17 +4156,17 @@
       <c r="F72">
         <v>0</v>
       </c>
-      <c r="G72" s="12">
+      <c r="G72" s="13">
         <v>0</v>
       </c>
       <c r="H72">
         <v>0</v>
       </c>
-      <c r="I72" s="12">
+      <c r="I72" s="13">
         <v>0</v>
       </c>
       <c r="J72">
-        <v>0</v>
+        <v>92815710810.606094</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -4127,8 +4174,8 @@
       <c r="L72">
         <v>0</v>
       </c>
-      <c r="M72" s="12">
-        <v>1.68759181528786E+16</v>
+      <c r="M72">
+        <v>0</v>
       </c>
       <c r="N72">
         <v>0</v>
@@ -4136,13 +4183,13 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B73" t="s">
-        <v>167</v>
-      </c>
-      <c r="C73">
-        <v>76.52</v>
+        <v>50</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C73" s="4">
+        <v>108.1378</v>
       </c>
       <c r="D73" s="4">
         <v>0</v>
@@ -4153,26 +4200,26 @@
       <c r="F73">
         <v>0</v>
       </c>
-      <c r="G73" s="12">
+      <c r="G73" s="13">
         <v>0</v>
       </c>
       <c r="H73">
         <v>0</v>
       </c>
-      <c r="I73" s="12">
+      <c r="I73" s="13">
         <v>0</v>
       </c>
       <c r="J73">
         <v>0</v>
       </c>
       <c r="K73">
-        <v>0</v>
+        <v>6626896422897450</v>
       </c>
       <c r="L73">
         <v>0</v>
       </c>
-      <c r="M73" s="12">
-        <v>6.7150804484951296E+17</v>
+      <c r="M73">
+        <v>0</v>
       </c>
       <c r="N73">
         <v>0</v>
@@ -4180,13 +4227,13 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>179</v>
+        <v>96</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C74">
-        <v>92.52</v>
+        <v>97</v>
+      </c>
+      <c r="C74" s="4">
+        <v>88.148200000000003</v>
       </c>
       <c r="D74" s="4">
         <v>0</v>
@@ -4197,14 +4244,14 @@
       <c r="F74">
         <v>0</v>
       </c>
-      <c r="G74" s="12">
+      <c r="G74" s="13">
         <v>0</v>
       </c>
       <c r="H74">
         <v>0</v>
       </c>
-      <c r="I74" s="12">
-        <v>0</v>
+      <c r="I74" s="13">
+        <v>7.99324851692944E+17</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -4215,8 +4262,8 @@
       <c r="L74">
         <v>0</v>
       </c>
-      <c r="M74" s="12">
-        <v>2.8116133288360998E+17</v>
+      <c r="M74">
+        <v>0</v>
       </c>
       <c r="N74">
         <v>0</v>
@@ -4224,13 +4271,13 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>169</v>
-      </c>
-      <c r="B75" t="s">
-        <v>170</v>
+        <v>98</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="C75">
-        <v>123.1293</v>
+        <v>76.094399999999993</v>
       </c>
       <c r="D75" s="4">
         <v>0</v>
@@ -4241,14 +4288,14 @@
       <c r="F75">
         <v>0</v>
       </c>
-      <c r="G75" s="12">
+      <c r="G75" s="13">
         <v>0</v>
       </c>
       <c r="H75">
         <v>0</v>
       </c>
-      <c r="I75" s="12">
-        <v>0</v>
+      <c r="I75" s="13">
+        <v>2.8727962844572001E+18</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -4259,8 +4306,8 @@
       <c r="L75">
         <v>0</v>
       </c>
-      <c r="M75" s="12">
-        <v>3.6515127709569602E+19</v>
+      <c r="M75">
+        <v>0</v>
       </c>
       <c r="N75">
         <v>0</v>
@@ -4268,13 +4315,13 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>171</v>
+        <v>101</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>172</v>
+        <v>102</v>
       </c>
       <c r="C76">
-        <v>106.1219</v>
+        <v>100.1589</v>
       </c>
       <c r="D76" s="4">
         <v>0</v>
@@ -4285,14 +4332,14 @@
       <c r="F76">
         <v>0</v>
       </c>
-      <c r="G76" s="12">
+      <c r="G76" s="13">
         <v>0</v>
       </c>
       <c r="H76">
         <v>0</v>
       </c>
-      <c r="I76" s="12">
-        <v>0</v>
+      <c r="I76" s="13">
+        <v>2.1374745930516401E+18</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -4303,22 +4350,22 @@
       <c r="L76">
         <v>0</v>
       </c>
-      <c r="M76" s="12">
-        <v>6.0524495405619302E+18</v>
+      <c r="M76">
+        <v>0</v>
       </c>
       <c r="N76">
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A77" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B77" t="s">
-        <v>174</v>
+      <c r="A77" t="s">
+        <v>103</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="C77">
-        <v>107.15</v>
+        <v>114.1855</v>
       </c>
       <c r="D77" s="4">
         <v>0</v>
@@ -4329,14 +4376,14 @@
       <c r="F77">
         <v>0</v>
       </c>
-      <c r="G77" s="12">
+      <c r="G77" s="13">
         <v>0</v>
       </c>
       <c r="H77">
         <v>0</v>
       </c>
-      <c r="I77" s="12">
-        <v>0</v>
+      <c r="I77" s="13">
+        <v>7.0407870654329997E+17</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -4347,8 +4394,8 @@
       <c r="L77">
         <v>0</v>
       </c>
-      <c r="M77" s="12">
-        <v>2.2778630803682E+17</v>
+      <c r="M77">
+        <v>0</v>
       </c>
       <c r="N77">
         <v>0</v>
@@ -4356,13 +4403,13 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B78" t="s">
-        <v>176</v>
+        <v>105</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="C78">
-        <v>126.58</v>
+        <v>136.23400000000001</v>
       </c>
       <c r="D78" s="4">
         <v>0</v>
@@ -4373,14 +4420,14 @@
       <c r="F78">
         <v>0</v>
       </c>
-      <c r="G78" s="12">
+      <c r="G78" s="13">
         <v>0</v>
       </c>
       <c r="H78">
         <v>0</v>
       </c>
-      <c r="I78" s="12">
-        <v>0</v>
+      <c r="I78" s="13">
+        <v>3.2841650965559202E+19</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -4391,22 +4438,22 @@
       <c r="L78">
         <v>0</v>
       </c>
-      <c r="M78" s="12">
-        <v>1.7506131971085699E+17</v>
+      <c r="M78">
+        <v>0</v>
       </c>
       <c r="N78">
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A79" s="3" t="s">
-        <v>177</v>
+      <c r="A79" t="s">
+        <v>107</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C79">
-        <v>161.03</v>
+        <v>170.24870000000001</v>
       </c>
       <c r="D79" s="4">
         <v>0</v>
@@ -4417,14 +4464,14 @@
       <c r="F79">
         <v>0</v>
       </c>
-      <c r="G79" s="12">
+      <c r="G79" s="13">
         <v>0</v>
       </c>
       <c r="H79">
-        <v>0</v>
-      </c>
-      <c r="I79" s="12">
-        <v>0</v>
+        <v>1375569322343650</v>
+      </c>
+      <c r="I79" s="13">
+        <v>5.9956572873684198E+17</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -4435,184 +4482,584 @@
       <c r="L79">
         <v>0</v>
       </c>
-      <c r="M79" s="12">
-        <v>6.98019330915034E+16</v>
-      </c>
-      <c r="N79">
-        <v>0</v>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79" s="13">
+        <v>2.48918362198186E+16</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
+        <v>108</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C80">
+        <v>170.24870000000001</v>
+      </c>
+      <c r="D80" s="4">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80" s="13">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80" s="13">
+        <v>4.4569487799906803E+17</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A81" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C81">
+        <v>204.3511</v>
+      </c>
+      <c r="D81" s="4">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81" s="13">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81" s="13">
+        <v>5.59185249900783E+18</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A82" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B82" t="s">
+        <v>162</v>
+      </c>
+      <c r="C82">
+        <v>57.09</v>
+      </c>
+      <c r="D82" s="4">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82" s="13">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82" s="13">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82" s="6">
+        <v>5062775445863580</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A83" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B83" t="s">
+        <v>163</v>
+      </c>
+      <c r="C83">
+        <v>76.52</v>
+      </c>
+      <c r="D83" s="4">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83" s="13">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83" s="13">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83" s="14">
+        <v>2.0145241345485402E+17</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A84" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C84">
+        <v>92.52</v>
+      </c>
+      <c r="D84" s="4">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84" s="13">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84" s="13">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84" s="14">
+        <v>8.43483998650832E+16</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>165</v>
+      </c>
+      <c r="B85" t="s">
+        <v>166</v>
+      </c>
+      <c r="C85">
+        <v>123.1293</v>
+      </c>
+      <c r="D85" s="4">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85" s="13">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85" s="13">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85" s="14">
+        <v>1.09545383128709E+19</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A86" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C86">
+        <v>106.1219</v>
+      </c>
+      <c r="D86" s="4">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86" s="13">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86" s="13">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86" s="14">
+        <v>1.8157348621685801E+18</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A87" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B87" t="s">
+        <v>170</v>
+      </c>
+      <c r="C87">
+        <v>107.15</v>
+      </c>
+      <c r="D87" s="4">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87" s="13">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87" s="13">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87" s="14">
+        <v>6.8335892411046E+16</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A88" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B88" t="s">
+        <v>172</v>
+      </c>
+      <c r="C88">
+        <v>126.58</v>
+      </c>
+      <c r="D88" s="4">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88" s="13">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88" s="13">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88" s="14">
+        <v>5.25183959132572E+16</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A89" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C89">
+        <v>161.03</v>
+      </c>
+      <c r="D89" s="4">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89" s="13">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89" s="13">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89" s="14">
+        <v>2.0940579927451E+16</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>178</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C90">
+        <v>156.26</v>
+      </c>
+      <c r="D90" s="4">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90" s="13">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90" s="13">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90" s="13">
+        <v>0</v>
+      </c>
+      <c r="N90" s="13">
+        <v>1.1865088354049E+16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>181</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C91">
+        <v>158.28110000000001</v>
+      </c>
+      <c r="D91" s="4">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91" s="13">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91" s="13">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91" s="13">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>3831134091148240</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
         <v>183</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B92" t="s">
         <v>184</v>
       </c>
-      <c r="C80">
-        <v>156.26</v>
-      </c>
-      <c r="D80" s="4">
-        <v>0</v>
-      </c>
-      <c r="E80">
-        <v>0</v>
-      </c>
-      <c r="F80">
-        <v>0</v>
-      </c>
-      <c r="G80" s="12">
-        <v>0</v>
-      </c>
-      <c r="H80">
-        <v>0</v>
-      </c>
-      <c r="I80" s="12">
-        <v>0</v>
-      </c>
-      <c r="J80">
-        <v>0</v>
-      </c>
-      <c r="K80">
-        <v>0</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80" s="12">
-        <v>0</v>
-      </c>
-      <c r="N80" s="12">
-        <v>1.1865088354049E+16</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>186</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C81">
-        <v>158.28110000000001</v>
-      </c>
-      <c r="D81" s="4">
-        <v>0</v>
-      </c>
-      <c r="E81">
-        <v>0</v>
-      </c>
-      <c r="F81">
-        <v>0</v>
-      </c>
-      <c r="G81" s="12">
-        <v>0</v>
-      </c>
-      <c r="H81">
-        <v>0</v>
-      </c>
-      <c r="I81" s="12">
-        <v>0</v>
-      </c>
-      <c r="J81">
-        <v>0</v>
-      </c>
-      <c r="K81">
-        <v>0</v>
-      </c>
-      <c r="L81">
-        <v>0</v>
-      </c>
-      <c r="M81" s="12">
-        <v>0</v>
-      </c>
-      <c r="N81">
-        <v>3831134091148240</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
-        <v>188</v>
-      </c>
-      <c r="B82" t="s">
-        <v>189</v>
-      </c>
-      <c r="C82">
+      <c r="C92">
         <v>122.12130000000001</v>
       </c>
-      <c r="D82" s="4">
-        <v>0</v>
-      </c>
-      <c r="E82">
-        <v>0</v>
-      </c>
-      <c r="F82">
-        <v>0</v>
-      </c>
-      <c r="G82" s="12">
-        <v>0</v>
-      </c>
-      <c r="H82">
-        <v>0</v>
-      </c>
-      <c r="I82" s="12">
-        <v>0</v>
-      </c>
-      <c r="J82">
-        <v>0</v>
-      </c>
-      <c r="K82">
-        <v>0</v>
-      </c>
-      <c r="L82">
-        <v>0</v>
-      </c>
-      <c r="M82" s="12">
-        <v>0</v>
-      </c>
-      <c r="N82" s="12">
+      <c r="D92" s="4">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92" s="13">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92" s="13">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92" s="13">
+        <v>0</v>
+      </c>
+      <c r="N92" s="13">
         <v>1.82639924706312E+16</v>
       </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A87" s="3"/>
-      <c r="B87" s="3"/>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A88" s="3"/>
-      <c r="B88" s="3"/>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A89" s="3"/>
-      <c r="B89" s="3"/>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A90" s="3"/>
-      <c r="B90" s="3"/>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A91" s="3"/>
-      <c r="B91" s="3"/>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A92" s="3"/>
-      <c r="B92" s="3"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" s="3"/>
@@ -44674,9 +45121,49 @@
       <c r="A10107" s="3"/>
       <c r="B10107" s="3"/>
     </row>
-    <row r="10108" spans="1:2" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10108" s="5"/>
+    <row r="10108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10108" s="3"/>
       <c r="B10108" s="3"/>
+    </row>
+    <row r="10109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10109" s="3"/>
+      <c r="B10109" s="3"/>
+    </row>
+    <row r="10110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10110" s="3"/>
+      <c r="B10110" s="3"/>
+    </row>
+    <row r="10111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10111" s="3"/>
+      <c r="B10111" s="3"/>
+    </row>
+    <row r="10112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10112" s="3"/>
+      <c r="B10112" s="3"/>
+    </row>
+    <row r="10113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10113" s="3"/>
+      <c r="B10113" s="3"/>
+    </row>
+    <row r="10114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10114" s="3"/>
+      <c r="B10114" s="3"/>
+    </row>
+    <row r="10115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10115" s="3"/>
+      <c r="B10115" s="3"/>
+    </row>
+    <row r="10116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10116" s="3"/>
+      <c r="B10116" s="3"/>
+    </row>
+    <row r="10117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10117" s="3"/>
+      <c r="B10117" s="3"/>
+    </row>
+    <row r="10118" spans="1:2" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10118" s="5"/>
+      <c r="B10118" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -44697,15 +45184,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B1" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -44722,6 +45209,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6030F4CF-2F4B-594A-AF9C-1A8D5AE0E84E}">
   <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="28.5" customWidth="1"/>
+    <col min="10" max="10" width="20.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -45066,27 +45558,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/src/indoor_environment_PyCHAM_setup/indoor_emi_pri_org_VBS.xlsx
+++ b/src/indoor_environment_PyCHAM_setup/indoor_emi_pri_org_VBS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Documents/GitHub/NCAS-BoxModellingToolkit/indoor_environment_PyCHAM_setup/src/indoor_environment_PyCHAM_setup/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livemanchesterac-my.sharepoint.com/personal/simon_omeara_manchester_ac_uk/Documents/GitHub/NCAS-BoxModellingToolkit/indoor_environment_PyCHAM_setup/src/indoor_environment_PyCHAM_setup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63E5A6B-FED0-9348-BDAA-8DBBD09655F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{2EF619C7-E479-174A-A447-3F7B7DC38047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5673C54A-211E-594B-B3B8-AA074746E0F4}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="5900" windowWidth="31060" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2460" yWindow="500" windowWidth="21860" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="indoor_emi" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="202">
   <si>
     <t>ACRYLONITRILE</t>
   </si>
@@ -605,9 +605,6 @@
     <t>in Table 1 they give the mass fraction of PM10 that is PM2.5 and they give the number of PM10  particles emitted/min emission rate, whilst their Figure  3 indicates that particle number concentration for washable filter bag less vacuum is dominated by PM2.5 (with a mean radius around 0.015 um), which is consistent with Figure 14 of doi.org/10.1016/j.atmosenv.2010.01.009. To get emission rate of PM2.5 particles in number/unit of time, first multiply the mass emission rate of PM10 (ug/s) from their Table 1 by 0.742 (the mass fraction that is PM2.5 from their Table 1), giving 0.93492 ug/s, then get mass of one particle of radius 0.015 um (radius set for vacuum cleaning for PM2.5 in indoor_emi sheet of this file), assuming a density of 1.4e-6 ug/um3, giving (using mass emission rate of PM10 (ug/s) from the washable filter bag less vacuum in their Table 1): (0.742*1.26)/((4./3.)*np.pi*0.015**3*1.4e-6) = 4.7e10 particles/s of PM2.5 with a mean radius of 0.015 um, likewise, the same can be done for PM2.5-PM10 assuming a mean radius of 2.5 um: ((1.-0.742)*1.26)/((4./3.)*np.pi*2.5**3*1.4e-6) = 3.5e3 particles/s of PM2.5-PM10 with a mean radius of 2.5 um</t>
   </si>
   <si>
-    <t>Frying (these values represent particles/ or molecules/s/person/meal or mole fraction of particles; particles from 10.1016/j.atmosenv.2010.01.009, using Table 2, which gives units in /min, and so /60 to convert to /s, e.g. 8.02e12 particles/60, gases from https://onlinelibrary.wiley.com/doi/full/10.1111/ina.12906 (Table 4), assuming stir fry lasted 15 minutes, e.g. for ethanol from table 4: ((67.e-3/46.0684)*6.022e23)/(15.*60.), note that citral not in MCM, so represented by limonene).  Particle radius of 0.03 um is suggested by Figure 12 of this reference. Black carbon to primary organic mole fractions estimated from Table 18 of http://dx.doi.org/10.1016/j.atmosenv.2013.01.061</t>
-  </si>
-  <si>
     <t>page 660 of https://doi.org/10.1080/15459624.2019.1643466 says the mass fraction of cleaning spray emitted on a single spray that goes airbourne (as gas and particles) rather than deposit on the surface to be cleaned is up to 1/3 (backed up by Figure S5 of https://doi.org/10.1016/j.ijheh.2023.114220), also mass of airbourne particles from cleaning spray is small (maximum mass fraction compared to airbourne particles+gas is 0.01%) compared to gas-phase from cleaning spray. Article https://doi.org/10.1016/j.ijheh.2023.114220 says the average emission rate (of total material (airbourne+deposited) is 1.6 g/s of cleaning spray). Suggest the following: convert the size-resolved plots of particle in the paper (Fig. 3 which suggests that the ratio in PM2.5 to PM10 is about 50:50) into an emission rate of particle containing a non-volatile material, and convert the mass of VOC released into individual components based on a mass-weighted ingredient list. This website (https://www.statista.com/statistics/304000/leading-brands-of-household-cleaners-in-the-uk/) suggests Dettol anti-bacterial surface cleanser is one of the best selling in the UK. The back of the dettol bottle lists: benzalkonium chloride as 0.096 % by mass, then there is also an unamed fragrance, sodium bicarbonate, sodium carbonate, sodium edetate, water, C9-C11 alkylpolyglycoside and C12-C16 Pareth-7. I think I can use this article (https://doi.org/10.1039/D2EA00054G) to get the VOC emission rates for commercial cleaning products, and the same article indicates that benzalkonium chloride is non-volatile (which the girolami techqnique estimates to have a density of 0.86g/cm^3), so this along with the sodium salts could represent the non-volatile particles</t>
   </si>
   <si>
@@ -643,6 +640,12 @@
   <si>
     <t>mean_rad_pm2</t>
   </si>
+  <si>
+    <t>this paper 10.1021/es202946w (emission rates of PM2.5 (ug/min) in Table 1 gives similar values to those reported in https://doi.org/10.1016/j.buildenv.2020.107059, though notes that in certan tests the emission rate was up to 3 orders of magnitude higher), it is noted that https://doi.org/10.1016/j.buildenv.2020.107059 does not account for particle loss to indoor surfaces, therefore values were increased by a factor 2.5 to correct for this</t>
+  </si>
+  <si>
+    <t>Frying (these values represent particles/ or molecules/s/person/meal or mole fraction of particles; particles from 10.1016/j.atmosenv.2010.01.009, using Table 2, which gives units in /min, and so /60 to convert to /s, e.g. 8.02e12 particles/60, gases from https://onlinelibrary.wiley.com/doi/full/10.1111/ina.12906 (Table 4), assuming stir fry lasted 15 minutes, e.g. for ethanol from table 4: ((67.e-3/46.0684)*6.022e23)/(15.*60.), note that citral not in MCM, so represented by limonene).  Particle radius of 0.03 um is suggested by Figure 12 of this reference (10.1016/j.atmosenv.2010.01.009). Black carbon to primary organic mole fractions estimated from Table 18 of http://dx.doi.org/10.1016/j.atmosenv.2013.01.061</t>
+  </si>
 </sst>
 </file>
 
@@ -673,8 +676,9 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Menlo"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -727,7 +731,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -747,6 +750,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1042,7 +1046,7 @@
     <col min="5" max="5" width="32.1640625" customWidth="1"/>
     <col min="6" max="6" width="22.33203125" customWidth="1"/>
     <col min="7" max="7" width="19.5" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.83203125" bestFit="1" customWidth="1"/>
@@ -1052,9 +1056,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7"/>
-      <c r="C1" s="8"/>
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="7"/>
       <c r="D1" s="15" t="s">
         <v>161</v>
       </c>
@@ -1062,103 +1066,103 @@
       <c r="F1" s="15"/>
       <c r="G1" s="15"/>
       <c r="H1" s="15"/>
-      <c r="I1" s="9"/>
+      <c r="I1" s="8"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="G2" s="9" t="s">
+      <c r="F2" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="M2" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="N2" s="9" t="s">
+      <c r="M2" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="N2" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="O2" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="P2" s="8" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>53</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C3" s="11">
-        <v>0</v>
-      </c>
-      <c r="D3" s="11">
+      <c r="C3" s="10">
+        <v>0</v>
+      </c>
+      <c r="D3" s="10">
         <v>0</v>
       </c>
       <c r="E3">
         <v>147166666666.67001</v>
       </c>
-      <c r="F3">
-        <v>133666666666.7</v>
-      </c>
-      <c r="G3" s="9">
-        <v>0</v>
-      </c>
-      <c r="H3" s="9">
-        <v>0</v>
-      </c>
-      <c r="I3" s="9">
-        <v>0</v>
-      </c>
-      <c r="J3" s="9">
+      <c r="F3" s="13">
+        <v>395510416666.67499</v>
+      </c>
+      <c r="G3" s="8">
+        <v>0</v>
+      </c>
+      <c r="H3" s="8">
+        <v>0</v>
+      </c>
+      <c r="I3" s="8">
+        <v>0</v>
+      </c>
+      <c r="J3" s="8">
         <v>1317449251.0999999</v>
       </c>
-      <c r="K3" s="9">
-        <v>0</v>
-      </c>
-      <c r="L3" s="13">
-        <v>47000000000</v>
-      </c>
-      <c r="M3" s="6">
-        <v>0</v>
-      </c>
-      <c r="N3" s="9">
-        <v>0</v>
-      </c>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
+      <c r="K3" s="8">
+        <v>0</v>
+      </c>
+      <c r="L3" s="12">
+        <v>117500000000</v>
+      </c>
+      <c r="M3" s="13">
+        <v>0</v>
+      </c>
+      <c r="N3" s="8">
+        <v>0</v>
+      </c>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
@@ -1203,8 +1207,8 @@
       <c r="N4">
         <v>0</v>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
@@ -1249,8 +1253,8 @@
       <c r="N5">
         <v>0</v>
       </c>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
@@ -1295,8 +1299,8 @@
       <c r="N6">
         <v>0</v>
       </c>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
@@ -1341,8 +1345,8 @@
       <c r="N7">
         <v>0</v>
       </c>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
@@ -1385,8 +1389,8 @@
       <c r="N8">
         <v>0</v>
       </c>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
@@ -1429,8 +1433,8 @@
       <c r="N9">
         <v>0</v>
       </c>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
@@ -1473,8 +1477,8 @@
       <c r="N10">
         <v>0</v>
       </c>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
@@ -1517,8 +1521,8 @@
       <c r="N11">
         <v>0</v>
       </c>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
@@ -1534,7 +1538,7 @@
         <v>3.9E-2</v>
       </c>
       <c r="F12">
-        <v>0.03</v>
+        <v>2.4E-2</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1560,20 +1564,20 @@
       <c r="N12">
         <v>0</v>
       </c>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="11" t="s">
         <v>52</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C13" s="11">
-        <v>0</v>
-      </c>
-      <c r="D13" s="11">
+      <c r="C13" s="10">
+        <v>0</v>
+      </c>
+      <c r="D13" s="10">
         <v>0</v>
       </c>
       <c r="E13">
@@ -1582,28 +1586,28 @@
       <c r="F13">
         <v>0</v>
       </c>
-      <c r="G13" s="9">
-        <v>0</v>
-      </c>
-      <c r="H13" s="9">
-        <v>0</v>
-      </c>
-      <c r="I13" s="9">
-        <v>0</v>
-      </c>
-      <c r="J13" s="9">
-        <v>0</v>
-      </c>
-      <c r="K13" s="9">
-        <v>0</v>
-      </c>
-      <c r="L13" s="13">
-        <v>0</v>
-      </c>
-      <c r="M13" s="6">
+      <c r="G13" s="8">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8">
+        <v>0</v>
+      </c>
+      <c r="L13" s="12">
+        <v>0</v>
+      </c>
+      <c r="M13" s="13">
         <v>2220766.6477938802</v>
       </c>
-      <c r="N13" s="9">
+      <c r="N13" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1993,8 +1997,8 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="12" t="s">
-        <v>191</v>
+      <c r="A23" s="11" t="s">
+        <v>190</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>146</v>
@@ -2026,10 +2030,10 @@
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="L23" s="13">
-        <v>3500</v>
-      </c>
-      <c r="M23" s="6">
+      <c r="L23" s="12">
+        <v>8750</v>
+      </c>
+      <c r="M23" s="13">
         <v>142129.06545880801</v>
       </c>
       <c r="N23">
@@ -2037,8 +2041,8 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="12" t="s">
-        <v>192</v>
+      <c r="A24" s="11" t="s">
+        <v>191</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>145</v>
@@ -2082,7 +2086,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>150</v>
@@ -2126,7 +2130,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>148</v>
@@ -2170,7 +2174,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>158</v>
@@ -2214,7 +2218,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28">
@@ -2256,7 +2260,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29">
@@ -2298,7 +2302,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30">
@@ -2340,7 +2344,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31">
@@ -2382,7 +2386,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>147</v>
@@ -2490,7 +2494,7 @@
       <c r="H34">
         <v>0</v>
       </c>
-      <c r="I34" s="13">
+      <c r="I34" s="12">
         <v>7.4580997301490002E+18</v>
       </c>
       <c r="J34">
@@ -2569,7 +2573,7 @@
       <c r="E36">
         <v>0</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="12">
         <v>9.7312788037883699E+17</v>
       </c>
       <c r="G36">
@@ -2578,7 +2582,7 @@
       <c r="H36">
         <v>0</v>
       </c>
-      <c r="I36" s="13">
+      <c r="I36" s="12">
         <v>5.8707519291711396E+21</v>
       </c>
       <c r="J36">
@@ -2613,10 +2617,10 @@
       <c r="E37">
         <v>0</v>
       </c>
-      <c r="F37" s="13">
+      <c r="F37" s="12">
         <v>8.9794231234033504E+16</v>
       </c>
-      <c r="G37" s="13">
+      <c r="G37" s="12">
         <v>2.2135322118157E+16</v>
       </c>
       <c r="H37">
@@ -2657,7 +2661,7 @@
       <c r="E38">
         <v>0</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38" s="12">
         <v>3.89976834891242E+16</v>
       </c>
       <c r="G38">
@@ -2666,7 +2670,7 @@
       <c r="H38">
         <v>0</v>
       </c>
-      <c r="I38" s="13">
+      <c r="I38" s="12">
         <v>0</v>
       </c>
       <c r="J38">
@@ -2701,16 +2705,16 @@
       <c r="E39">
         <v>0</v>
       </c>
-      <c r="F39" s="13">
+      <c r="F39" s="12">
         <v>2.56692630577486E+16</v>
       </c>
-      <c r="G39" s="13">
+      <c r="G39" s="12">
         <v>1.57964695739991E+16</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
-      <c r="I39" s="13">
+      <c r="I39" s="12">
         <v>1.7593729219433099E+19</v>
       </c>
       <c r="J39">
@@ -2745,7 +2749,7 @@
       <c r="E40">
         <v>0</v>
       </c>
-      <c r="F40" s="13">
+      <c r="F40" s="12">
         <v>1.47464788921009E+16</v>
       </c>
       <c r="G40">
@@ -2754,7 +2758,7 @@
       <c r="H40">
         <v>0</v>
       </c>
-      <c r="I40" s="13">
+      <c r="I40" s="12">
         <v>1.88E+19</v>
       </c>
       <c r="J40">
@@ -2798,7 +2802,7 @@
       <c r="H41">
         <v>0</v>
       </c>
-      <c r="I41" s="13">
+      <c r="I41" s="12">
         <v>0</v>
       </c>
       <c r="J41">
@@ -2830,19 +2834,19 @@
       <c r="D42" s="4">
         <v>0</v>
       </c>
-      <c r="E42" s="13">
+      <c r="E42" s="12">
         <v>6494526650446900</v>
       </c>
-      <c r="F42" s="13">
-        <v>0</v>
-      </c>
-      <c r="G42" s="13">
+      <c r="F42" s="12">
+        <v>0</v>
+      </c>
+      <c r="G42" s="12">
         <v>0</v>
       </c>
       <c r="H42">
         <v>0</v>
       </c>
-      <c r="I42" s="13">
+      <c r="I42" s="12">
         <v>0</v>
       </c>
       <c r="J42">
@@ -2874,19 +2878,19 @@
       <c r="D43" s="4">
         <v>0</v>
       </c>
-      <c r="E43" s="13">
+      <c r="E43" s="12">
         <v>4.05206901116216E+16</v>
       </c>
       <c r="F43">
         <v>3438038799255520</v>
       </c>
-      <c r="G43" s="13">
+      <c r="G43" s="12">
         <v>0</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
-      <c r="I43" s="13">
+      <c r="I43" s="12">
         <v>2.7450925701073101E+18</v>
       </c>
       <c r="J43">
@@ -2924,13 +2928,13 @@
       <c r="F44">
         <v>6683556305501490</v>
       </c>
-      <c r="G44" s="13">
+      <c r="G44" s="12">
         <v>0</v>
       </c>
       <c r="H44">
         <v>0</v>
       </c>
-      <c r="I44" s="13">
+      <c r="I44" s="12">
         <v>0</v>
       </c>
       <c r="J44">
@@ -2968,13 +2972,13 @@
       <c r="F45">
         <v>0</v>
       </c>
-      <c r="G45" s="13">
+      <c r="G45" s="12">
         <v>0</v>
       </c>
       <c r="H45">
         <v>0</v>
       </c>
-      <c r="I45" s="13">
+      <c r="I45" s="12">
         <v>0</v>
       </c>
       <c r="J45">
@@ -3009,16 +3013,16 @@
       <c r="E46">
         <v>3855758491862170</v>
       </c>
-      <c r="F46" s="13">
-        <v>0</v>
-      </c>
-      <c r="G46" s="13">
+      <c r="F46" s="12">
+        <v>0</v>
+      </c>
+      <c r="G46" s="12">
         <v>0</v>
       </c>
       <c r="H46">
         <v>0</v>
       </c>
-      <c r="I46" s="13">
+      <c r="I46" s="12">
         <v>0</v>
       </c>
       <c r="J46">
@@ -3050,19 +3054,19 @@
       <c r="D47" s="4">
         <v>0</v>
       </c>
-      <c r="E47" s="13">
+      <c r="E47" s="12">
         <v>2.30306213752953E+16</v>
       </c>
       <c r="F47">
         <v>0</v>
       </c>
-      <c r="G47" s="13">
+      <c r="G47" s="12">
         <v>0</v>
       </c>
       <c r="H47">
         <v>0</v>
       </c>
-      <c r="I47" s="13">
+      <c r="I47" s="12">
         <v>0</v>
       </c>
       <c r="J47">
@@ -3097,16 +3101,16 @@
       <c r="E48">
         <v>4972719602159980</v>
       </c>
-      <c r="F48" s="13">
-        <v>0</v>
-      </c>
-      <c r="G48" s="13">
+      <c r="F48" s="12">
+        <v>0</v>
+      </c>
+      <c r="G48" s="12">
         <v>0</v>
       </c>
       <c r="H48">
         <v>0</v>
       </c>
-      <c r="I48" s="13">
+      <c r="I48" s="12">
         <v>2.8332937268120801E+18</v>
       </c>
       <c r="J48">
@@ -3144,7 +3148,7 @@
       <c r="F49">
         <v>0</v>
       </c>
-      <c r="G49" s="13">
+      <c r="G49" s="12">
         <v>0</v>
       </c>
       <c r="H49">
@@ -3185,16 +3189,16 @@
       <c r="E50">
         <v>1181757319581150</v>
       </c>
-      <c r="F50" s="13">
-        <v>0</v>
-      </c>
-      <c r="G50" s="13">
+      <c r="F50" s="12">
+        <v>0</v>
+      </c>
+      <c r="G50" s="12">
         <v>0</v>
       </c>
       <c r="H50">
         <v>0</v>
       </c>
-      <c r="I50" s="13">
+      <c r="I50" s="12">
         <v>0</v>
       </c>
       <c r="J50">
@@ -3232,13 +3236,13 @@
       <c r="F51">
         <v>0</v>
       </c>
-      <c r="G51" s="13">
+      <c r="G51" s="12">
         <v>0</v>
       </c>
       <c r="H51">
         <v>0</v>
       </c>
-      <c r="I51" s="13">
+      <c r="I51" s="12">
         <v>0</v>
       </c>
       <c r="J51">
@@ -3273,16 +3277,16 @@
       <c r="E52">
         <v>671238157522096</v>
       </c>
-      <c r="F52" s="13">
-        <v>0</v>
-      </c>
-      <c r="G52" s="13">
+      <c r="F52" s="12">
+        <v>0</v>
+      </c>
+      <c r="G52" s="12">
         <v>0</v>
       </c>
       <c r="H52">
         <v>0</v>
       </c>
-      <c r="I52" s="13">
+      <c r="I52" s="12">
         <v>0</v>
       </c>
       <c r="J52">
@@ -3320,13 +3324,13 @@
       <c r="F53">
         <v>0</v>
       </c>
-      <c r="G53" s="13">
+      <c r="G53" s="12">
         <v>0</v>
       </c>
       <c r="H53">
         <v>0</v>
       </c>
-      <c r="I53" s="13">
+      <c r="I53" s="12">
         <v>0</v>
       </c>
       <c r="J53">
@@ -3361,16 +3365,16 @@
       <c r="E54">
         <v>459291306269878</v>
       </c>
-      <c r="F54" s="13">
-        <v>0</v>
-      </c>
-      <c r="G54" s="13">
+      <c r="F54" s="12">
+        <v>0</v>
+      </c>
+      <c r="G54" s="12">
         <v>0</v>
       </c>
       <c r="H54">
         <v>0</v>
       </c>
-      <c r="I54" s="13">
+      <c r="I54" s="12">
         <v>0</v>
       </c>
       <c r="J54">
@@ -3408,13 +3412,13 @@
       <c r="F55">
         <v>0</v>
       </c>
-      <c r="G55" s="13">
+      <c r="G55" s="12">
         <v>0</v>
       </c>
       <c r="H55">
         <v>0</v>
       </c>
-      <c r="I55" s="13">
+      <c r="I55" s="12">
         <v>0</v>
       </c>
       <c r="J55">
@@ -3449,16 +3453,16 @@
       <c r="E56">
         <v>115049465648389</v>
       </c>
-      <c r="F56" s="13">
-        <v>0</v>
-      </c>
-      <c r="G56" s="13">
+      <c r="F56" s="12">
+        <v>0</v>
+      </c>
+      <c r="G56" s="12">
         <v>0</v>
       </c>
       <c r="H56">
         <v>0</v>
       </c>
-      <c r="I56" s="13">
+      <c r="I56" s="12">
         <v>0</v>
       </c>
       <c r="J56">
@@ -3496,13 +3500,13 @@
       <c r="F57">
         <v>0</v>
       </c>
-      <c r="G57" s="13">
+      <c r="G57" s="12">
         <v>0</v>
       </c>
       <c r="H57">
         <v>0</v>
       </c>
-      <c r="I57" s="13">
+      <c r="I57" s="12">
         <v>0</v>
       </c>
       <c r="J57">
@@ -3537,16 +3541,16 @@
       <c r="E58">
         <v>885189865959984</v>
       </c>
-      <c r="F58" s="13">
-        <v>0</v>
-      </c>
-      <c r="G58" s="13">
+      <c r="F58" s="12">
+        <v>0</v>
+      </c>
+      <c r="G58" s="12">
         <v>0</v>
       </c>
       <c r="H58">
         <v>0</v>
       </c>
-      <c r="I58" s="13">
+      <c r="I58" s="12">
         <v>0</v>
       </c>
       <c r="J58">
@@ -3584,13 +3588,13 @@
       <c r="F59">
         <v>0</v>
       </c>
-      <c r="G59" s="13">
+      <c r="G59" s="12">
         <v>0</v>
       </c>
       <c r="H59">
         <v>0</v>
       </c>
-      <c r="I59" s="13">
+      <c r="I59" s="12">
         <v>0</v>
       </c>
       <c r="J59">
@@ -3625,16 +3629,16 @@
       <c r="E60">
         <v>213476443143224</v>
       </c>
-      <c r="F60" s="13">
-        <v>0</v>
-      </c>
-      <c r="G60" s="13">
+      <c r="F60" s="12">
+        <v>0</v>
+      </c>
+      <c r="G60" s="12">
         <v>0</v>
       </c>
       <c r="H60">
         <v>0</v>
       </c>
-      <c r="I60" s="13">
+      <c r="I60" s="12">
         <v>0</v>
       </c>
       <c r="J60">
@@ -3672,13 +3676,13 @@
       <c r="F61">
         <v>0</v>
       </c>
-      <c r="G61" s="13">
+      <c r="G61" s="12">
         <v>0</v>
       </c>
       <c r="H61">
         <v>0</v>
       </c>
-      <c r="I61" s="13">
+      <c r="I61" s="12">
         <v>0</v>
       </c>
       <c r="J61">
@@ -3713,16 +3717,16 @@
       <c r="E62">
         <v>1422603851820030</v>
       </c>
-      <c r="F62" s="13">
-        <v>0</v>
-      </c>
-      <c r="G62" s="13">
+      <c r="F62" s="12">
+        <v>0</v>
+      </c>
+      <c r="G62" s="12">
         <v>0</v>
       </c>
       <c r="H62">
         <v>0</v>
       </c>
-      <c r="I62" s="13">
+      <c r="I62" s="12">
         <v>0</v>
       </c>
       <c r="J62">
@@ -3760,13 +3764,13 @@
       <c r="F63">
         <v>0</v>
       </c>
-      <c r="G63" s="13">
+      <c r="G63" s="12">
         <v>0</v>
       </c>
       <c r="H63">
         <v>0</v>
       </c>
-      <c r="I63" s="13">
+      <c r="I63" s="12">
         <v>0</v>
       </c>
       <c r="J63">
@@ -3801,16 +3805,16 @@
       <c r="E64">
         <v>4144017962239770</v>
       </c>
-      <c r="F64" s="13">
-        <v>0</v>
-      </c>
-      <c r="G64" s="13">
+      <c r="F64" s="12">
+        <v>0</v>
+      </c>
+      <c r="G64" s="12">
         <v>0</v>
       </c>
       <c r="H64">
         <v>0</v>
       </c>
-      <c r="I64" s="13">
+      <c r="I64" s="12">
         <v>0</v>
       </c>
       <c r="J64">
@@ -3848,13 +3852,13 @@
       <c r="F65">
         <v>0</v>
       </c>
-      <c r="G65" s="13">
+      <c r="G65" s="12">
         <v>0</v>
       </c>
       <c r="H65">
         <v>0</v>
       </c>
-      <c r="I65" s="13">
+      <c r="I65" s="12">
         <v>0</v>
       </c>
       <c r="J65">
@@ -3889,16 +3893,16 @@
       <c r="E66">
         <v>9898568768132020</v>
       </c>
-      <c r="F66" s="13">
-        <v>0</v>
-      </c>
-      <c r="G66" s="13">
+      <c r="F66" s="12">
+        <v>0</v>
+      </c>
+      <c r="G66" s="12">
         <v>0</v>
       </c>
       <c r="H66">
         <v>0</v>
       </c>
-      <c r="I66" s="13">
+      <c r="I66" s="12">
         <v>0</v>
       </c>
       <c r="J66">
@@ -3936,13 +3940,13 @@
       <c r="F67">
         <v>0</v>
       </c>
-      <c r="G67" s="13">
+      <c r="G67" s="12">
         <v>0</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
-      <c r="I67" s="13">
+      <c r="I67" s="12">
         <v>0</v>
       </c>
       <c r="J67">
@@ -3980,10 +3984,10 @@
       <c r="F68">
         <v>2996005239351240</v>
       </c>
-      <c r="G68" s="13">
-        <v>0</v>
-      </c>
-      <c r="H68" s="13">
+      <c r="G68" s="12">
+        <v>0</v>
+      </c>
+      <c r="H68" s="12">
         <v>6.13935499867058E+16</v>
       </c>
       <c r="I68">
@@ -4024,7 +4028,7 @@
       <c r="F69">
         <v>0</v>
       </c>
-      <c r="G69" s="13">
+      <c r="G69" s="12">
         <v>0</v>
       </c>
       <c r="H69">
@@ -4068,13 +4072,13 @@
       <c r="F70">
         <v>0</v>
       </c>
-      <c r="G70" s="13">
+      <c r="G70" s="12">
         <v>0</v>
       </c>
       <c r="H70">
         <v>0</v>
       </c>
-      <c r="I70" s="13">
+      <c r="I70" s="12">
         <v>0</v>
       </c>
       <c r="J70">
@@ -4112,16 +4116,16 @@
       <c r="F71">
         <v>0</v>
       </c>
-      <c r="G71" s="13">
+      <c r="G71" s="12">
         <v>0</v>
       </c>
       <c r="H71">
         <v>0</v>
       </c>
-      <c r="I71" s="13">
-        <v>0</v>
-      </c>
-      <c r="J71" s="13">
+      <c r="I71" s="12">
+        <v>0</v>
+      </c>
+      <c r="J71" s="12">
         <v>4.7866168828592902E+17</v>
       </c>
       <c r="K71">
@@ -4156,13 +4160,13 @@
       <c r="F72">
         <v>0</v>
       </c>
-      <c r="G72" s="13">
+      <c r="G72" s="12">
         <v>0</v>
       </c>
       <c r="H72">
         <v>0</v>
       </c>
-      <c r="I72" s="13">
+      <c r="I72" s="12">
         <v>0</v>
       </c>
       <c r="J72">
@@ -4200,13 +4204,13 @@
       <c r="F73">
         <v>0</v>
       </c>
-      <c r="G73" s="13">
+      <c r="G73" s="12">
         <v>0</v>
       </c>
       <c r="H73">
         <v>0</v>
       </c>
-      <c r="I73" s="13">
+      <c r="I73" s="12">
         <v>0</v>
       </c>
       <c r="J73">
@@ -4244,13 +4248,13 @@
       <c r="F74">
         <v>0</v>
       </c>
-      <c r="G74" s="13">
+      <c r="G74" s="12">
         <v>0</v>
       </c>
       <c r="H74">
         <v>0</v>
       </c>
-      <c r="I74" s="13">
+      <c r="I74" s="12">
         <v>7.99324851692944E+17</v>
       </c>
       <c r="J74">
@@ -4288,13 +4292,13 @@
       <c r="F75">
         <v>0</v>
       </c>
-      <c r="G75" s="13">
+      <c r="G75" s="12">
         <v>0</v>
       </c>
       <c r="H75">
         <v>0</v>
       </c>
-      <c r="I75" s="13">
+      <c r="I75" s="12">
         <v>2.8727962844572001E+18</v>
       </c>
       <c r="J75">
@@ -4332,13 +4336,13 @@
       <c r="F76">
         <v>0</v>
       </c>
-      <c r="G76" s="13">
+      <c r="G76" s="12">
         <v>0</v>
       </c>
       <c r="H76">
         <v>0</v>
       </c>
-      <c r="I76" s="13">
+      <c r="I76" s="12">
         <v>2.1374745930516401E+18</v>
       </c>
       <c r="J76">
@@ -4376,13 +4380,13 @@
       <c r="F77">
         <v>0</v>
       </c>
-      <c r="G77" s="13">
+      <c r="G77" s="12">
         <v>0</v>
       </c>
       <c r="H77">
         <v>0</v>
       </c>
-      <c r="I77" s="13">
+      <c r="I77" s="12">
         <v>7.0407870654329997E+17</v>
       </c>
       <c r="J77">
@@ -4420,13 +4424,13 @@
       <c r="F78">
         <v>0</v>
       </c>
-      <c r="G78" s="13">
+      <c r="G78" s="12">
         <v>0</v>
       </c>
       <c r="H78">
         <v>0</v>
       </c>
-      <c r="I78" s="13">
+      <c r="I78" s="12">
         <v>3.2841650965559202E+19</v>
       </c>
       <c r="J78">
@@ -4464,13 +4468,13 @@
       <c r="F79">
         <v>0</v>
       </c>
-      <c r="G79" s="13">
+      <c r="G79" s="12">
         <v>0</v>
       </c>
       <c r="H79">
         <v>1375569322343650</v>
       </c>
-      <c r="I79" s="13">
+      <c r="I79" s="12">
         <v>5.9956572873684198E+17</v>
       </c>
       <c r="J79">
@@ -4485,7 +4489,7 @@
       <c r="M79">
         <v>0</v>
       </c>
-      <c r="N79" s="13">
+      <c r="N79" s="12">
         <v>2.48918362198186E+16</v>
       </c>
     </row>
@@ -4508,13 +4512,13 @@
       <c r="F80">
         <v>0</v>
       </c>
-      <c r="G80" s="13">
+      <c r="G80" s="12">
         <v>0</v>
       </c>
       <c r="H80">
         <v>0</v>
       </c>
-      <c r="I80" s="13">
+      <c r="I80" s="12">
         <v>4.4569487799906803E+17</v>
       </c>
       <c r="J80">
@@ -4552,13 +4556,13 @@
       <c r="F81">
         <v>0</v>
       </c>
-      <c r="G81" s="13">
+      <c r="G81" s="12">
         <v>0</v>
       </c>
       <c r="H81">
         <v>0</v>
       </c>
-      <c r="I81" s="13">
+      <c r="I81" s="12">
         <v>5.59185249900783E+18</v>
       </c>
       <c r="J81">
@@ -4596,13 +4600,13 @@
       <c r="F82">
         <v>0</v>
       </c>
-      <c r="G82" s="13">
+      <c r="G82" s="12">
         <v>0</v>
       </c>
       <c r="H82">
         <v>0</v>
       </c>
-      <c r="I82" s="13">
+      <c r="I82" s="12">
         <v>0</v>
       </c>
       <c r="J82">
@@ -4614,7 +4618,7 @@
       <c r="L82">
         <v>0</v>
       </c>
-      <c r="M82" s="6">
+      <c r="M82" s="13">
         <v>5062775445863580</v>
       </c>
       <c r="N82">
@@ -4640,13 +4644,13 @@
       <c r="F83">
         <v>0</v>
       </c>
-      <c r="G83" s="13">
+      <c r="G83" s="12">
         <v>0</v>
       </c>
       <c r="H83">
         <v>0</v>
       </c>
-      <c r="I83" s="13">
+      <c r="I83" s="12">
         <v>0</v>
       </c>
       <c r="J83">
@@ -4684,13 +4688,13 @@
       <c r="F84">
         <v>0</v>
       </c>
-      <c r="G84" s="13">
+      <c r="G84" s="12">
         <v>0</v>
       </c>
       <c r="H84">
         <v>0</v>
       </c>
-      <c r="I84" s="13">
+      <c r="I84" s="12">
         <v>0</v>
       </c>
       <c r="J84">
@@ -4728,13 +4732,13 @@
       <c r="F85">
         <v>0</v>
       </c>
-      <c r="G85" s="13">
+      <c r="G85" s="12">
         <v>0</v>
       </c>
       <c r="H85">
         <v>0</v>
       </c>
-      <c r="I85" s="13">
+      <c r="I85" s="12">
         <v>0</v>
       </c>
       <c r="J85">
@@ -4772,13 +4776,13 @@
       <c r="F86">
         <v>0</v>
       </c>
-      <c r="G86" s="13">
+      <c r="G86" s="12">
         <v>0</v>
       </c>
       <c r="H86">
         <v>0</v>
       </c>
-      <c r="I86" s="13">
+      <c r="I86" s="12">
         <v>0</v>
       </c>
       <c r="J86">
@@ -4816,13 +4820,13 @@
       <c r="F87">
         <v>0</v>
       </c>
-      <c r="G87" s="13">
+      <c r="G87" s="12">
         <v>0</v>
       </c>
       <c r="H87">
         <v>0</v>
       </c>
-      <c r="I87" s="13">
+      <c r="I87" s="12">
         <v>0</v>
       </c>
       <c r="J87">
@@ -4860,13 +4864,13 @@
       <c r="F88">
         <v>0</v>
       </c>
-      <c r="G88" s="13">
+      <c r="G88" s="12">
         <v>0</v>
       </c>
       <c r="H88">
         <v>0</v>
       </c>
-      <c r="I88" s="13">
+      <c r="I88" s="12">
         <v>0</v>
       </c>
       <c r="J88">
@@ -4904,13 +4908,13 @@
       <c r="F89">
         <v>0</v>
       </c>
-      <c r="G89" s="13">
+      <c r="G89" s="12">
         <v>0</v>
       </c>
       <c r="H89">
         <v>0</v>
       </c>
-      <c r="I89" s="13">
+      <c r="I89" s="12">
         <v>0</v>
       </c>
       <c r="J89">
@@ -4948,13 +4952,13 @@
       <c r="F90">
         <v>0</v>
       </c>
-      <c r="G90" s="13">
+      <c r="G90" s="12">
         <v>0</v>
       </c>
       <c r="H90">
         <v>0</v>
       </c>
-      <c r="I90" s="13">
+      <c r="I90" s="12">
         <v>0</v>
       </c>
       <c r="J90">
@@ -4966,10 +4970,10 @@
       <c r="L90">
         <v>0</v>
       </c>
-      <c r="M90" s="13">
-        <v>0</v>
-      </c>
-      <c r="N90" s="13">
+      <c r="M90" s="12">
+        <v>0</v>
+      </c>
+      <c r="N90" s="12">
         <v>1.1865088354049E+16</v>
       </c>
     </row>
@@ -4992,13 +4996,13 @@
       <c r="F91">
         <v>0</v>
       </c>
-      <c r="G91" s="13">
+      <c r="G91" s="12">
         <v>0</v>
       </c>
       <c r="H91">
         <v>0</v>
       </c>
-      <c r="I91" s="13">
+      <c r="I91" s="12">
         <v>0</v>
       </c>
       <c r="J91">
@@ -5010,7 +5014,7 @@
       <c r="L91">
         <v>0</v>
       </c>
-      <c r="M91" s="13">
+      <c r="M91" s="12">
         <v>0</v>
       </c>
       <c r="N91">
@@ -5036,13 +5040,13 @@
       <c r="F92">
         <v>0</v>
       </c>
-      <c r="G92" s="13">
+      <c r="G92" s="12">
         <v>0</v>
       </c>
       <c r="H92">
         <v>0</v>
       </c>
-      <c r="I92" s="13">
+      <c r="I92" s="12">
         <v>0</v>
       </c>
       <c r="J92">
@@ -5054,10 +5058,10 @@
       <c r="L92">
         <v>0</v>
       </c>
-      <c r="M92" s="13">
-        <v>0</v>
-      </c>
-      <c r="N92" s="13">
+      <c r="M92" s="12">
+        <v>0</v>
+      </c>
+      <c r="N92" s="12">
         <v>1.82639924706312E+16</v>
       </c>
     </row>
@@ -45187,7 +45191,7 @@
         <v>153</v>
       </c>
       <c r="B1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -45553,7 +45557,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A1424E3-65E6-4D4E-8617-9B434C5DD01D}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -45579,6 +45583,11 @@
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/src/indoor_environment_PyCHAM_setup/indoor_emi_pri_org_VBS.xlsx
+++ b/src/indoor_environment_PyCHAM_setup/indoor_emi_pri_org_VBS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livemanchesterac-my.sharepoint.com/personal/simon_omeara_manchester_ac_uk/Documents/GitHub/NCAS-BoxModellingToolkit/indoor_environment_PyCHAM_setup/src/indoor_environment_PyCHAM_setup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{2EF619C7-E479-174A-A447-3F7B7DC38047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12471697-6F5D-45C6-B4C4-01B84BD84897}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{2EF619C7-E479-174A-A447-3F7B7DC38047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F4AEA92-6BCF-4106-A999-19A387A4ACFD}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="120" windowWidth="16188" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="840" windowWidth="18924" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="indoor_emi" sheetId="1" r:id="rId1"/>
@@ -1136,10 +1136,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>147166666666.67001</v>
+        <v>300000000000</v>
       </c>
       <c r="F3" s="13">
-        <v>3955104166666.75</v>
+        <v>2000000000000</v>
       </c>
       <c r="G3" s="8">
         <v>0</v>

--- a/src/indoor_environment_PyCHAM_setup/indoor_emi_pri_org_VBS.xlsx
+++ b/src/indoor_environment_PyCHAM_setup/indoor_emi_pri_org_VBS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livemanchesterac-my.sharepoint.com/personal/simon_omeara_manchester_ac_uk/Documents/GitHub/NCAS-BoxModellingToolkit/indoor_environment_PyCHAM_setup/src/indoor_environment_PyCHAM_setup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="13_ncr:1_{2EF619C7-E479-174A-A447-3F7B7DC38047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE263203-6F97-1842-A4E5-A17C4D03D045}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{30D5AEC0-A9C1-5C44-A108-36C9A8FF0C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63CA9033-BB42-4C43-9E1E-B82F3BCC37B7}"/>
   <bookViews>
-    <workbookView xWindow="5920" yWindow="4620" windowWidth="22780" windowHeight="15680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60" yWindow="500" windowWidth="24280" windowHeight="12020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="indoor_emi" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="208">
   <si>
     <t>ACRYLONITRILE</t>
   </si>
@@ -641,12 +641,6 @@
     <t>this paper 10.1021/es202946w (emission rates of PM2.5 (ug/min) in Table 1 gives similar values to those reported in https://doi.org/10.1016/j.buildenv.2020.107059, though notes that in certan tests the emission rate was up to 3 orders of magnitude higher), it is noted that https://doi.org/10.1016/j.buildenv.2020.107059 does not account for particle loss to indoor surfaces, therefore values were increased by a factor 2.5 to correct for this</t>
   </si>
   <si>
-    <t>Frying (these values represent particles/ or molecules/s/person/meal or mole fraction of particles; particles from 10.1016/j.atmosenv.2010.01.009, using Table 2, which gives units in /min, and so /60 to convert to /s, e.g. 8.02e12 particles/60, gases from https://onlinelibrary.wiley.com/doi/full/10.1111/ina.12906 (Table 4), assuming stir fry lasted 15 minutes, e.g. for ethanol from table 4: ((67.e-3/46.0684)*6.022e23)/(15.*60.), note that citral not in MCM, so represented by limonene).  Particle radius of 0.03 um is suggested by Figure 12 of this reference (10.1016/j.atmosenv.2010.01.009). Black carbon to primary organic mole fractions estimated from Table 18 of http://dx.doi.org/10.1016/j.atmosenv.2013.01.061</t>
-  </si>
-  <si>
-    <t>candle burning (doi.org/10.1016/j.jaerosci.2008.10.005), which shows in Fig. 10 that most particle mass is in candles with a diameter less than 160 nm, the arithmetic mean of steady burn PM2.5 mass emission factor for their candle 1 and candle 2 in Table 1 is 1.635 mg/h, which converts to 4.54e-7 g/s. Then need to convert to particles/s by dividing by the mass of one particle, and Fig 10. shows that most mass during steady burn has particle radius around 50 nm, which gives a volume of 4/3*np.pi*50e-7**3 cm^3 = 5.24e-16 cm^3, and the density is based on Table 3 that indicates that potassium nitrate is a main mass contributor to candle particles, which is supported by the internet that says potassium nitrate is used to help the wick burn, then 5.24e-16*2.11 cm^3=1.11e-15g per particle, so the particle emission rate is 4.54e-7 g/s/1.11e-15g/particle = 4.09e8 particle/s</t>
-  </si>
-  <si>
     <t>POT_NIT_ind_pm0</t>
   </si>
   <si>
@@ -658,12 +652,24 @@
   <si>
     <t>POT_NIT_ind_pm2</t>
   </si>
+  <si>
+    <t>candle burning (doi.org/10.1016/j.jaerosci.2008.10.005), which shows in Fig. 10 that most particle mass is in candles with a diameter less than 160 nm, the arithmetic mean of steady burn PM2.5 mass emission factor for their candle 1 and candle 2 in Table 1 is 1.635 mg/h, which converts to 4.54e-7 g/s. Then need to convert to particles/s by dividing by the mass of one particle, and Fig 10. shows that most mass during steady burn has particle radius around 50 nm, which gives a volume of 4/3*np.pi*50e-7**3 cm^3 = 5.24e-16 cm^3, and the density is based on Table 3 that indicates that potassium nitrate is a main mass contributor to candle particles, which is supported by the internet that says potassium nitrate is used to help the wick burn, then 5.24e-16*2.11 cm^3=1.11e-15g per particle, so the particle emission rate is 4.54e-7 g/s/1.11e-15g/particle = 4.09e8 particle/s. Note that this emission rate, and combined particle radius has been tested against the lab observations in their Fig. 6 for wall deposition of particles rates typical of chambers</t>
+  </si>
+  <si>
+    <t>dirty gas fire place, with pconc tuned to PM2.5 values seen for combustion household</t>
+  </si>
+  <si>
+    <t>Frying (these values represent particles/ or molecules/s or mole fraction of particles; particles from 10.1016/j.atmosenv.2010.01.009, where ultrafine particles have radius 50 nm or less, using Table 2, which gives units in /min, and so /60 to convert to /s, e.g. 7.66e12 particles/60=1.3e11 /s. Note that for some of the particle emission in Table 2 for frying, the number emitted has a contribution from larger than ultrafine particles. Fig 6c of https://doi.org/10.1016/j.atmosenv.2009.03.044 shows that mass peak for frying occurs around 0.3um diameter, so this determines the radius of the second size bin here. In addition, Table 6 of https://doi.org/10.1016/j.atmosenv.2009.03.044 reports a peak mass concentration of particles (which is generated at full gas stove power) of 118 ug/m3, which is reproduced by the values below in the test simulation for reproducing their experimental conditions, with inputs saved in fry_test_against_doiporgslash10p1016slashjpatmosenvp2009p03p044. Note that using a mean radius for the second size bin of 0.1 um led to quick transfer of these particles to the smaller size bin, presumably because of evaporation of volatiles. Results from testing frying inputs are saved in frying_test_doi_10p1016dashjpatmosenvp2010p01p009. Gases from https://onlinelibrary.wiley.com/doi/full/10.1111/ina.12906 (Table 4), assuming stir fry lasted 15 minutes, e.g. for ethanol from table 4: ((67.e-3/46.0684)*6.022e23)/(15.*60.), note that citral not in MCM, so represented by limonene). Black carbon to primary organic mole fractions estimated from Table 18 of http://dx.doi.org/10.1016/j.atmosenv.2013.01.061</t>
+  </si>
+  <si>
+    <t>flickering candle, from Table 2 of doi.org/10.1111/ina.12909 (Candle 5), 1.5e13/3600 =  5.17e9 particles/s are generated, whilst their Fig 2. suggests a small fraction of this number is in a larger mode. Table 2 indicates these particles are composed of elemental carbon (with a molar mass of 12.01 g/mol), Table 2 also says that 4346/3600= 1.21 ug/s of black carbon is released. Fig 2 shows that most particle mass is in the larger mode particles, so assuming 1.20 ug/s comes from the large mode and 0.01 ug/s comes from the small mode, and that of the total number emitted 0.1 % is in the larger mode, then each large mode particle must contain 1.20/(5.17e9*0.001) =  2.32e-7 ug of carbon. Carbon as graphite has a density of 2.26 g/cm^3, which means each particle has a volume 2.32e-13 g/particle/2.26 g/cm^3 = 1.03e-13 cm^3, which is a radius of (V*3/(4.*np.pi))**(1./3.) 2.91e-5 cm, which is 0.291 um. Using the same template for the smaller particles gives ((0.01/(5.17e9*0.999)*1.e-6/2.26*3.)/(4.*np.pi))**(1./3.)=5.89e-7cm or 0.00589 um. However, this value for the larger particles does not get anywhere near the mass concentrations of PM2.5 seen in the combustion household of INGENIOUS. Instead, the mean radius was set to 0.45 um, which is consistent with the Candle 5 plot of mass-size distribution in Fig.2 of  https://doi.org/10.1111/ina.12909, whilst the number concentration was tuned to give emission factors of PM2.5 consistent with Table 1 of https://doi.org/10.1016/j.envint.2011.07.009, which report possible emisssion factors from candles of 15 mg/g. Table 2 of https://doi.org/10.1111/ina.12909 shows a typical burn rate of 5g/hour for candles, so one can do the calculation: 15.(mg/g)*1.e3(mg to ug)*5.(g/hr)/3600(per hr to per s) = 21 ug/s, whilst the values used here give a rate of (4./3.)*np.pi*0.45e-4**3(cm^3/particle)*2.26(g/cm^3)*1.e6(g/particle to ug/particle)*25850000(particles/s)=22 ug/s. This value is the same order of magnitude as reported in Table 1 for candle II of https://doi.org/10.1016/j.jaerosci.2008.10.005, which reports that during sooting (flickering), mass emission rates can be around 25 mg/hour, which equates to 25*1.e3(mg to ug)/3600(hour to s) = 7 ug/s, which is also the mass emission factor reported from a real home in Table 2 of https://doi.org/10.1016/j.buildenv.2021.108422</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -691,6 +697,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Menlo"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -734,7 +746,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -764,10 +776,11 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1055,7 +1068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P10121"/>
+  <dimension ref="A1:R10121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.5" customWidth="1"/>
@@ -1063,7 +1076,7 @@
     <col min="3" max="3" width="32.1640625" style="4" customWidth="1"/>
     <col min="4" max="4" width="29" style="4" customWidth="1"/>
     <col min="5" max="5" width="32.1640625" customWidth="1"/>
-    <col min="6" max="6" width="22.33203125" customWidth="1"/>
+    <col min="6" max="6" width="35.6640625" customWidth="1"/>
     <col min="7" max="7" width="19.5" customWidth="1"/>
     <col min="8" max="8" width="19.6640625" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
@@ -1072,22 +1085,25 @@
     <col min="12" max="12" width="15.1640625" customWidth="1"/>
     <col min="13" max="13" width="16.33203125" customWidth="1"/>
     <col min="14" max="14" width="12.6640625" customWidth="1"/>
+    <col min="15" max="15" width="18.6640625" customWidth="1"/>
+    <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="7"/>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
       <c r="I1" s="8"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
         <v>21</v>
       </c>
@@ -1104,7 +1120,7 @@
         <v>185</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>136</v>
@@ -1134,10 +1150,16 @@
         <v>155</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+        <v>204</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>53</v>
       </c>
@@ -1153,8 +1175,8 @@
       <c r="E3">
         <v>300000000000</v>
       </c>
-      <c r="F3" s="13">
-        <v>2000000000000</v>
+      <c r="F3" s="16">
+        <v>129666666666.666</v>
       </c>
       <c r="G3" s="8">
         <v>0</v>
@@ -1184,10 +1206,16 @@
         <v>0</v>
       </c>
       <c r="P3" s="16">
-        <v>409000000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+        <v>400000000</v>
+      </c>
+      <c r="Q3" s="16">
+        <v>5164830000</v>
+      </c>
+      <c r="R3" s="15">
+        <v>1200000000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>64</v>
       </c>
@@ -1236,8 +1264,14 @@
       <c r="P4" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q4" s="16">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>149</v>
       </c>
@@ -1286,8 +1320,14 @@
       <c r="P5" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q5" s="16">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>143</v>
       </c>
@@ -1336,8 +1376,14 @@
       <c r="P6" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q6" s="16">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>158</v>
       </c>
@@ -1386,13 +1432,19 @@
       <c r="P7" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="16">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C8">
         <v>101.1</v>
@@ -1436,8 +1488,14 @@
       <c r="P8" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="16">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>83</v>
       </c>
@@ -1484,8 +1542,14 @@
       <c r="P9" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="16">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>80</v>
       </c>
@@ -1532,8 +1596,14 @@
       <c r="P10" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="16">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>84</v>
       </c>
@@ -1580,8 +1650,14 @@
       <c r="P11" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="16">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>94</v>
       </c>
@@ -1628,8 +1704,14 @@
       <c r="P12" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="16">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>62</v>
       </c>
@@ -1675,8 +1757,14 @@
       <c r="P13" s="8">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="16">
+        <v>5.8900000000000003E-3</v>
+      </c>
+      <c r="R13">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>52</v>
       </c>
@@ -1692,8 +1780,8 @@
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14">
-        <v>0</v>
+      <c r="F14" s="16">
+        <v>4000000000</v>
       </c>
       <c r="G14" s="8">
         <v>0</v>
@@ -1722,11 +1810,17 @@
       <c r="O14" s="8">
         <v>0</v>
       </c>
-      <c r="P14" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="16">
+        <v>9000000</v>
+      </c>
+      <c r="Q14" s="16">
+        <v>25850000</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>65</v>
       </c>
@@ -1743,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>9.0899999999999995E-2</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1775,8 +1869,14 @@
       <c r="P15" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="16">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>151</v>
       </c>
@@ -1825,8 +1925,14 @@
       <c r="P16" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>144</v>
       </c>
@@ -1875,8 +1981,14 @@
       <c r="P17" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="16">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>159</v>
       </c>
@@ -1925,13 +2037,19 @@
       <c r="P18" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="16">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C19">
         <v>101.1</v>
@@ -1973,10 +2091,16 @@
         <v>0</v>
       </c>
       <c r="P19" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="16">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>82</v>
       </c>
@@ -2023,8 +2147,14 @@
       <c r="P20" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="16">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>81</v>
       </c>
@@ -2039,7 +2169,7 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>0.18634239288307916</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2071,8 +2201,14 @@
       <c r="P21" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="16">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>85</v>
       </c>
@@ -2087,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>0.39348119099491646</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -2119,8 +2255,14 @@
       <c r="P22" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="16">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>86</v>
       </c>
@@ -2135,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>0.32927641612200437</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -2167,8 +2309,14 @@
       <c r="P23" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="16">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>63</v>
       </c>
@@ -2182,7 +2330,7 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -2212,10 +2360,16 @@
         <v>0</v>
       </c>
       <c r="P24" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+        <v>0.2</v>
+      </c>
+      <c r="Q24" s="16">
+        <v>0.45</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
         <v>189</v>
       </c>
@@ -2264,8 +2418,14 @@
       <c r="P25" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="16">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
         <v>190</v>
       </c>
@@ -2314,8 +2474,14 @@
       <c r="P26" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="16">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>191</v>
       </c>
@@ -2364,8 +2530,14 @@
       <c r="P27" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="16">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>192</v>
       </c>
@@ -2414,8 +2586,14 @@
       <c r="P28" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="16">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>193</v>
       </c>
@@ -2464,13 +2642,19 @@
       <c r="P29" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="16">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C30" s="4">
         <v>0</v>
@@ -2514,8 +2698,14 @@
       <c r="P30" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="16">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>194</v>
       </c>
@@ -2562,8 +2752,14 @@
       <c r="P31" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="16">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>195</v>
       </c>
@@ -2610,8 +2806,14 @@
       <c r="P32" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="16">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>196</v>
       </c>
@@ -2658,8 +2860,14 @@
       <c r="P33" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="16">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>197</v>
       </c>
@@ -2706,8 +2914,14 @@
       <c r="P34" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="16">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>198</v>
       </c>
@@ -2753,8 +2967,14 @@
       <c r="P35" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="16">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>54</v>
       </c>
@@ -2803,8 +3023,14 @@
       <c r="P36" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q36" s="16">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>38</v>
       </c>
@@ -2853,8 +3079,14 @@
       <c r="P37" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q37" s="16">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
@@ -2903,8 +3135,14 @@
       <c r="P38" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="16">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>23</v>
       </c>
@@ -2953,8 +3191,14 @@
       <c r="P39" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="16">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>25</v>
       </c>
@@ -3003,8 +3247,14 @@
       <c r="P40" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="16">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>27</v>
       </c>
@@ -3053,8 +3303,14 @@
       <c r="P41" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="16">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>29</v>
       </c>
@@ -3103,8 +3359,14 @@
       <c r="P42" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="16">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>31</v>
       </c>
@@ -3153,8 +3415,14 @@
       <c r="P43" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="16">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>36</v>
       </c>
@@ -3203,8 +3471,14 @@
       <c r="P44" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="16">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>11</v>
       </c>
@@ -3253,8 +3527,14 @@
       <c r="P45" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="16">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>12</v>
       </c>
@@ -3303,8 +3583,14 @@
       <c r="P46" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="16">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>13</v>
       </c>
@@ -3353,8 +3639,14 @@
       <c r="P47" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="16">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>0</v>
       </c>
@@ -3403,8 +3695,14 @@
       <c r="P48" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="16">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>14</v>
       </c>
@@ -3453,8 +3751,14 @@
       <c r="P49" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="16">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>2</v>
       </c>
@@ -3503,8 +3807,14 @@
       <c r="P50" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="16">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>1</v>
       </c>
@@ -3553,8 +3863,14 @@
       <c r="P51" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="16">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3603,8 +3919,14 @@
       <c r="P52" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="16">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>20</v>
       </c>
@@ -3653,8 +3975,14 @@
       <c r="P53" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="16">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>15</v>
       </c>
@@ -3703,8 +4031,14 @@
       <c r="P54" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="16">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>16</v>
       </c>
@@ -3753,8 +4087,14 @@
       <c r="P55" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="16">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>4</v>
       </c>
@@ -3803,8 +4143,14 @@
       <c r="P56" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="16">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -3853,8 +4199,14 @@
       <c r="P57" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="16">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
         <v>5</v>
       </c>
@@ -3903,8 +4255,14 @@
       <c r="P58" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="16">
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>57</v>
       </c>
@@ -3953,8 +4311,14 @@
       <c r="P59" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="16">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>58</v>
       </c>
@@ -4003,8 +4367,14 @@
       <c r="P60" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="16">
+        <v>0</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>6</v>
       </c>
@@ -4053,8 +4423,14 @@
       <c r="P61" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="16">
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>18</v>
       </c>
@@ -4103,8 +4479,14 @@
       <c r="P62" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="16">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>18</v>
       </c>
@@ -4153,8 +4535,14 @@
       <c r="P63" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="16">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>7</v>
       </c>
@@ -4203,8 +4591,14 @@
       <c r="P64" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="16">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>59</v>
       </c>
@@ -4253,8 +4647,14 @@
       <c r="P65" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="16">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
         <v>60</v>
       </c>
@@ -4303,8 +4703,14 @@
       <c r="P66" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="16">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>8</v>
       </c>
@@ -4353,8 +4759,14 @@
       <c r="P67" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="16">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>61</v>
       </c>
@@ -4403,8 +4815,14 @@
       <c r="P68" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="16">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>9</v>
       </c>
@@ -4453,8 +4871,14 @@
       <c r="P69" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="16">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>10</v>
       </c>
@@ -4503,8 +4927,14 @@
       <c r="P70" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="16">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>33</v>
       </c>
@@ -4553,8 +4983,14 @@
       <c r="P71" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="16">
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
         <v>42</v>
       </c>
@@ -4603,8 +5039,14 @@
       <c r="P72" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="16">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>44</v>
       </c>
@@ -4653,8 +5095,14 @@
       <c r="P73" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="16">
+        <v>0</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>46</v>
       </c>
@@ -4703,8 +5151,14 @@
       <c r="P74" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="16">
+        <v>0</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
         <v>48</v>
       </c>
@@ -4753,8 +5207,14 @@
       <c r="P75" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="16">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>50</v>
       </c>
@@ -4803,8 +5263,14 @@
       <c r="P76" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="16">
+        <v>0</v>
+      </c>
+      <c r="R76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
         <v>96</v>
       </c>
@@ -4853,8 +5319,14 @@
       <c r="P77" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="16">
+        <v>0</v>
+      </c>
+      <c r="R77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>98</v>
       </c>
@@ -4903,8 +5375,14 @@
       <c r="P78" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q78" s="16">
+        <v>0</v>
+      </c>
+      <c r="R78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>101</v>
       </c>
@@ -4953,8 +5431,14 @@
       <c r="P79" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q79" s="16">
+        <v>0</v>
+      </c>
+      <c r="R79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>103</v>
       </c>
@@ -5003,8 +5487,14 @@
       <c r="P80" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="16">
+        <v>0</v>
+      </c>
+      <c r="R80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
         <v>105</v>
       </c>
@@ -5053,8 +5543,14 @@
       <c r="P81" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="16">
+        <v>0</v>
+      </c>
+      <c r="R81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>107</v>
       </c>
@@ -5103,8 +5599,14 @@
       <c r="P82" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="16">
+        <v>0</v>
+      </c>
+      <c r="R82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>108</v>
       </c>
@@ -5153,8 +5655,14 @@
       <c r="P83" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="16">
+        <v>0</v>
+      </c>
+      <c r="R83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
         <v>110</v>
       </c>
@@ -5203,8 +5711,14 @@
       <c r="P84" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="16">
+        <v>0</v>
+      </c>
+      <c r="R84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
         <v>176</v>
       </c>
@@ -5253,8 +5767,14 @@
       <c r="P85" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="16">
+        <v>0</v>
+      </c>
+      <c r="R85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
         <v>175</v>
       </c>
@@ -5303,8 +5823,14 @@
       <c r="P86" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="16">
+        <v>0</v>
+      </c>
+      <c r="R86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
         <v>174</v>
       </c>
@@ -5353,8 +5879,14 @@
       <c r="P87" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="16">
+        <v>0</v>
+      </c>
+      <c r="R87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>164</v>
       </c>
@@ -5403,8 +5935,14 @@
       <c r="P88" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="16">
+        <v>0</v>
+      </c>
+      <c r="R88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
         <v>166</v>
       </c>
@@ -5453,8 +5991,14 @@
       <c r="P89" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="16">
+        <v>0</v>
+      </c>
+      <c r="R89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
         <v>168</v>
       </c>
@@ -5503,8 +6047,14 @@
       <c r="P90" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="16">
+        <v>0</v>
+      </c>
+      <c r="R90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
         <v>170</v>
       </c>
@@ -5553,8 +6103,14 @@
       <c r="P91" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="16">
+        <v>0</v>
+      </c>
+      <c r="R91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
         <v>172</v>
       </c>
@@ -5603,8 +6159,14 @@
       <c r="P92" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="16">
+        <v>0</v>
+      </c>
+      <c r="R92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>177</v>
       </c>
@@ -5653,8 +6215,14 @@
       <c r="P93" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="16">
+        <v>0</v>
+      </c>
+      <c r="R93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>180</v>
       </c>
@@ -5703,8 +6271,14 @@
       <c r="P94" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="16">
+        <v>0</v>
+      </c>
+      <c r="R94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>182</v>
       </c>
@@ -5753,8 +6327,14 @@
       <c r="P95" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="16">
+        <v>0</v>
+      </c>
+      <c r="R95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
     </row>
